--- a/data/nzd0151/nzd0151.xlsx
+++ b/data/nzd0151/nzd0151.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O610"/>
+  <dimension ref="A1:O611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31564,6 +31564,57 @@
       <c r="O610" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>393.05</v>
+      </c>
+      <c r="C611" t="n">
+        <v>382.22</v>
+      </c>
+      <c r="D611" t="n">
+        <v>372.24</v>
+      </c>
+      <c r="E611" t="n">
+        <v>364.69</v>
+      </c>
+      <c r="F611" t="n">
+        <v>374.92</v>
+      </c>
+      <c r="G611" t="n">
+        <v>379.58</v>
+      </c>
+      <c r="H611" t="n">
+        <v>379.26</v>
+      </c>
+      <c r="I611" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="J611" t="n">
+        <v>385.57</v>
+      </c>
+      <c r="K611" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="L611" t="n">
+        <v>382.24</v>
+      </c>
+      <c r="M611" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="N611" t="n">
+        <v>383.41</v>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31578,7 +31629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37831,6 +37882,16 @@
       </c>
       <c r="B625" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -37999,28 +38060,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1867192652396081</v>
+        <v>-0.191089772216638</v>
       </c>
       <c r="J2" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K2" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L2" t="n">
-        <v>0.045167660465537</v>
+        <v>0.04703965847351399</v>
       </c>
       <c r="M2" t="n">
-        <v>5.042629609225093</v>
+        <v>5.05639813099402</v>
       </c>
       <c r="N2" t="n">
-        <v>39.02966406461363</v>
+        <v>39.24973972415172</v>
       </c>
       <c r="O2" t="n">
-        <v>6.247372572899237</v>
+        <v>6.264961270762312</v>
       </c>
       <c r="P2" t="n">
-        <v>411.1467437399231</v>
+        <v>411.1930528798205</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -38081,28 +38142,28 @@
         <v>0.0257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.218729468555572</v>
+        <v>-0.2200749040739647</v>
       </c>
       <c r="J3" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K3" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05716817411640085</v>
+        <v>0.05799195136014768</v>
       </c>
       <c r="M3" t="n">
-        <v>5.308759300028282</v>
+        <v>5.306957113662533</v>
       </c>
       <c r="N3" t="n">
-        <v>41.78414674127837</v>
+        <v>41.74256784280698</v>
       </c>
       <c r="O3" t="n">
-        <v>6.464065805766396</v>
+        <v>6.460848848472388</v>
       </c>
       <c r="P3" t="n">
-        <v>392.0268255594269</v>
+        <v>392.0410815626713</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -38163,28 +38224,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.245183466779981</v>
+        <v>-0.2468364389013205</v>
       </c>
       <c r="J4" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K4" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08903949952880563</v>
+        <v>0.09032538191424011</v>
       </c>
       <c r="M4" t="n">
-        <v>4.688425475324697</v>
+        <v>4.689369777647479</v>
       </c>
       <c r="N4" t="n">
-        <v>32.56988529308291</v>
+        <v>32.55712472531845</v>
       </c>
       <c r="O4" t="n">
-        <v>5.707003179697985</v>
+        <v>5.705885095698865</v>
       </c>
       <c r="P4" t="n">
-        <v>383.6746340857455</v>
+        <v>383.692148693917</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -38245,28 +38306,28 @@
         <v>0.0317</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2208281617959266</v>
+        <v>-0.2231611490822439</v>
       </c>
       <c r="J5" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K5" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0836323605741367</v>
+        <v>0.08531198130322448</v>
       </c>
       <c r="M5" t="n">
-        <v>4.341603199598587</v>
+        <v>4.348870986941954</v>
       </c>
       <c r="N5" t="n">
-        <v>28.29575807998276</v>
+        <v>28.3303127146071</v>
       </c>
       <c r="O5" t="n">
-        <v>5.319375722768863</v>
+        <v>5.322622728937971</v>
       </c>
       <c r="P5" t="n">
-        <v>377.5341316921068</v>
+        <v>377.5588516239565</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -38327,28 +38388,28 @@
         <v>0.0356</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2043118791664189</v>
+        <v>-0.2064874518180865</v>
       </c>
       <c r="J6" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K6" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06624016273127276</v>
+        <v>0.0676445877741596</v>
       </c>
       <c r="M6" t="n">
-        <v>4.39919861561733</v>
+        <v>4.404909460845535</v>
       </c>
       <c r="N6" t="n">
-        <v>31.16147928298246</v>
+        <v>31.18078176255716</v>
       </c>
       <c r="O6" t="n">
-        <v>5.582246795241362</v>
+        <v>5.583975444301054</v>
       </c>
       <c r="P6" t="n">
-        <v>386.8521392986613</v>
+        <v>386.8751912921285</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -38409,28 +38470,28 @@
         <v>0.0358</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2495999730630788</v>
+        <v>-0.2516521478637227</v>
       </c>
       <c r="J7" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K7" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09892507295026565</v>
+        <v>0.1005278736829177</v>
       </c>
       <c r="M7" t="n">
-        <v>4.196797719453802</v>
+        <v>4.203148683231971</v>
       </c>
       <c r="N7" t="n">
-        <v>30.05111735888553</v>
+        <v>30.06448190132321</v>
       </c>
       <c r="O7" t="n">
-        <v>5.481889944069064</v>
+        <v>5.483108780730436</v>
       </c>
       <c r="P7" t="n">
-        <v>392.3303964776338</v>
+        <v>392.3521409687047</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -38491,28 +38552,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2524719011452976</v>
+        <v>-0.2546970549682769</v>
       </c>
       <c r="J8" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K8" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1146389617396267</v>
+        <v>0.1165080658164273</v>
       </c>
       <c r="M8" t="n">
-        <v>3.886693831738638</v>
+        <v>3.893471935758455</v>
       </c>
       <c r="N8" t="n">
-        <v>26.06941543711532</v>
+        <v>26.10031034521446</v>
       </c>
       <c r="O8" t="n">
-        <v>5.105821720067723</v>
+        <v>5.108846283185124</v>
       </c>
       <c r="P8" t="n">
-        <v>392.6118550610277</v>
+        <v>392.6354324080547</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -38573,28 +38634,28 @@
         <v>0.0367</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1171611199717871</v>
+        <v>-0.1193908318393014</v>
       </c>
       <c r="J9" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K9" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03396576650444882</v>
+        <v>0.03522443414875998</v>
       </c>
       <c r="M9" t="n">
-        <v>3.462659338498733</v>
+        <v>3.467376389753466</v>
       </c>
       <c r="N9" t="n">
-        <v>20.67450671783533</v>
+        <v>20.71454770432206</v>
       </c>
       <c r="O9" t="n">
-        <v>4.546922774562521</v>
+        <v>4.551323730995419</v>
       </c>
       <c r="P9" t="n">
-        <v>392.4240970047058</v>
+        <v>392.4477226479884</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -38655,28 +38716,28 @@
         <v>0.0357</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05422289168896846</v>
+        <v>-0.05621625094150117</v>
       </c>
       <c r="J10" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K10" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01029172134121215</v>
+        <v>0.01104961353666001</v>
       </c>
       <c r="M10" t="n">
-        <v>3.021438167320281</v>
+        <v>3.024296294266076</v>
       </c>
       <c r="N10" t="n">
-        <v>14.97274967180088</v>
+        <v>15.00729440443899</v>
       </c>
       <c r="O10" t="n">
-        <v>3.869463744732709</v>
+        <v>3.873924935312891</v>
       </c>
       <c r="P10" t="n">
-        <v>393.0135095479096</v>
+        <v>393.034630839553</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -38737,28 +38798,28 @@
         <v>0.0406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07899301462032289</v>
+        <v>0.07677208611986636</v>
       </c>
       <c r="J11" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K11" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01898147893539626</v>
+        <v>0.01793513595964746</v>
       </c>
       <c r="M11" t="n">
-        <v>3.222221410010359</v>
+        <v>3.226456424905579</v>
       </c>
       <c r="N11" t="n">
-        <v>17.07817918341944</v>
+        <v>17.12353445174426</v>
       </c>
       <c r="O11" t="n">
-        <v>4.132575369357399</v>
+        <v>4.138059261507048</v>
       </c>
       <c r="P11" t="n">
-        <v>390.8976098878235</v>
+        <v>390.9211424640602</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -38819,28 +38880,28 @@
         <v>0.0457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06637655844517387</v>
+        <v>-0.06846307032712191</v>
       </c>
       <c r="J12" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K12" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0138606649023113</v>
+        <v>0.01472782837799413</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23751587437365</v>
+        <v>3.240755919103185</v>
       </c>
       <c r="N12" t="n">
-        <v>16.59971799980011</v>
+        <v>16.63724736163899</v>
       </c>
       <c r="O12" t="n">
-        <v>4.074275150232261</v>
+        <v>4.078878198921731</v>
       </c>
       <c r="P12" t="n">
-        <v>390.2832965673049</v>
+        <v>390.3054048881808</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -38901,28 +38962,28 @@
         <v>0.0416</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09302635069761818</v>
+        <v>-0.09528066715674773</v>
       </c>
       <c r="J13" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K13" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03037967001048159</v>
+        <v>0.03177320043031495</v>
       </c>
       <c r="M13" t="n">
-        <v>3.026111333493283</v>
+        <v>3.0304442212148</v>
       </c>
       <c r="N13" t="n">
-        <v>14.62674397694268</v>
+        <v>14.67834002787329</v>
       </c>
       <c r="O13" t="n">
-        <v>3.824492643076031</v>
+        <v>3.831232181410217</v>
       </c>
       <c r="P13" t="n">
-        <v>389.3706693796981</v>
+        <v>389.3945557289998</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -38983,28 +39044,28 @@
         <v>0.0362</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.111694672518649</v>
+        <v>-0.1140534384515466</v>
       </c>
       <c r="J14" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K14" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02380981821975026</v>
+        <v>0.02481311787679152</v>
       </c>
       <c r="M14" t="n">
-        <v>4.210302828342258</v>
+        <v>4.212030652753958</v>
       </c>
       <c r="N14" t="n">
-        <v>27.08696234576862</v>
+        <v>27.12529723414292</v>
       </c>
       <c r="O14" t="n">
-        <v>5.204513651223198</v>
+        <v>5.208195199312611</v>
       </c>
       <c r="P14" t="n">
-        <v>393.4663862219553</v>
+        <v>393.4913792999084</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -39046,7 +39107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O610"/>
+  <dimension ref="A1:O611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86019,6 +86080,83 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>-36.68000070680074,174.74902295248305</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>-36.68068507502776,174.7493696791877</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>-36.681397269989134,174.74961708864703</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>-36.68209331417289,174.74988487103977</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-36.682779669355895,174.75016509352403</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>-36.68345036713532,174.75045044283263</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>-36.68412916422574,174.75073292403883</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>-36.684801569505545,174.7510561435933</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>-36.685475132809366,174.7513752460864</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>-36.686146376200064,174.75166615841215</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>-36.68681004596929,174.7519760442164</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>-36.6874676409207,174.7523352329846</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>-36.68810665473184,174.75275051313466</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0151/nzd0151.xlsx
+++ b/data/nzd0151/nzd0151.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O611"/>
+  <dimension ref="A1:O613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31574,7 +31574,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>393.05</v>
+        <v>395.37</v>
       </c>
       <c r="C611" t="n">
         <v>382.22</v>
@@ -31615,6 +31615,108 @@
       <c r="O611" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>392.6</v>
+      </c>
+      <c r="C612" t="n">
+        <v>382.46</v>
+      </c>
+      <c r="D612" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="E612" t="n">
+        <v>365.14</v>
+      </c>
+      <c r="F612" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="G612" t="n">
+        <v>380.26</v>
+      </c>
+      <c r="H612" t="n">
+        <v>379.18</v>
+      </c>
+      <c r="I612" t="n">
+        <v>382.89</v>
+      </c>
+      <c r="J612" t="n">
+        <v>385.69</v>
+      </c>
+      <c r="K612" t="n">
+        <v>386.97</v>
+      </c>
+      <c r="L612" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="M612" t="n">
+        <v>381.21</v>
+      </c>
+      <c r="N612" t="n">
+        <v>384.3</v>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>392.95</v>
+      </c>
+      <c r="C613" t="n">
+        <v>383.13</v>
+      </c>
+      <c r="D613" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="E613" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="F613" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="G613" t="n">
+        <v>381.62</v>
+      </c>
+      <c r="H613" t="n">
+        <v>380.41</v>
+      </c>
+      <c r="I613" t="n">
+        <v>384.42</v>
+      </c>
+      <c r="J613" t="n">
+        <v>386.68</v>
+      </c>
+      <c r="K613" t="n">
+        <v>388.07</v>
+      </c>
+      <c r="L613" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="M613" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="N613" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -31629,7 +31731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B626"/>
+  <dimension ref="A1:B628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37892,6 +37994,26 @@
       </c>
       <c r="B626" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>
@@ -38060,28 +38182,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.191089772216638</v>
+        <v>-0.1991265084899545</v>
       </c>
       <c r="J2" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K2" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04703965847351399</v>
+        <v>0.05061455237079715</v>
       </c>
       <c r="M2" t="n">
-        <v>5.05639813099402</v>
+        <v>5.080537097861868</v>
       </c>
       <c r="N2" t="n">
-        <v>39.24973972415172</v>
+        <v>39.61217537208392</v>
       </c>
       <c r="O2" t="n">
-        <v>6.264961270762312</v>
+        <v>6.293820411489664</v>
       </c>
       <c r="P2" t="n">
-        <v>411.1930528798205</v>
+        <v>411.2782920431013</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -38142,28 +38264,28 @@
         <v>0.0257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2200749040739647</v>
+        <v>-0.222347003577582</v>
       </c>
       <c r="J3" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K3" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05799195136014768</v>
+        <v>0.05946683063610658</v>
       </c>
       <c r="M3" t="n">
-        <v>5.306957113662533</v>
+        <v>5.301287393252552</v>
       </c>
       <c r="N3" t="n">
-        <v>41.74256784280698</v>
+        <v>41.64522865786561</v>
       </c>
       <c r="O3" t="n">
-        <v>6.460848848472388</v>
+        <v>6.453311449005511</v>
       </c>
       <c r="P3" t="n">
-        <v>392.0410815626713</v>
+        <v>392.0651777064397</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -38224,28 +38346,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2468364389013205</v>
+        <v>-0.2499881655245778</v>
       </c>
       <c r="J4" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K4" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09032538191424011</v>
+        <v>0.09283361666333134</v>
       </c>
       <c r="M4" t="n">
-        <v>4.689369777647479</v>
+        <v>4.690507842857882</v>
       </c>
       <c r="N4" t="n">
-        <v>32.55712472531845</v>
+        <v>32.52549708075304</v>
       </c>
       <c r="O4" t="n">
-        <v>5.705885095698865</v>
+        <v>5.703112928984752</v>
       </c>
       <c r="P4" t="n">
-        <v>383.692148693917</v>
+        <v>383.7255735585837</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -38306,28 +38428,28 @@
         <v>0.0317</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2231611490822439</v>
+        <v>-0.2270252142103505</v>
       </c>
       <c r="J5" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K5" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08531198130322448</v>
+        <v>0.08827629230368372</v>
       </c>
       <c r="M5" t="n">
-        <v>4.348870986941954</v>
+        <v>4.358691133648885</v>
       </c>
       <c r="N5" t="n">
-        <v>28.3303127146071</v>
+        <v>28.35115246294549</v>
       </c>
       <c r="O5" t="n">
-        <v>5.322622728937971</v>
+        <v>5.324580026907802</v>
       </c>
       <c r="P5" t="n">
-        <v>377.5588516239565</v>
+        <v>377.5998308910513</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -38388,28 +38510,28 @@
         <v>0.0356</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2064874518180865</v>
+        <v>-0.2104976042526554</v>
       </c>
       <c r="J6" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K6" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0676445877741596</v>
+        <v>0.0703193444750928</v>
       </c>
       <c r="M6" t="n">
-        <v>4.404909460845535</v>
+        <v>4.414391151699925</v>
       </c>
       <c r="N6" t="n">
-        <v>31.18078176255716</v>
+        <v>31.20014848269736</v>
       </c>
       <c r="O6" t="n">
-        <v>5.583975444301054</v>
+        <v>5.585709308825278</v>
       </c>
       <c r="P6" t="n">
-        <v>386.8751912921285</v>
+        <v>386.9177199472888</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -38470,28 +38592,28 @@
         <v>0.0358</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2516521478637227</v>
+        <v>-0.2548030653285478</v>
       </c>
       <c r="J7" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K7" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1005278736829177</v>
+        <v>0.1032206621761591</v>
       </c>
       <c r="M7" t="n">
-        <v>4.203148683231971</v>
+        <v>4.209626821507888</v>
       </c>
       <c r="N7" t="n">
-        <v>30.06448190132321</v>
+        <v>30.04219180451723</v>
       </c>
       <c r="O7" t="n">
-        <v>5.483108780730436</v>
+        <v>5.481075788977674</v>
       </c>
       <c r="P7" t="n">
-        <v>392.3521409687047</v>
+        <v>392.3855570903647</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -38552,28 +38674,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2546970549682769</v>
+        <v>-0.2587333301638322</v>
       </c>
       <c r="J8" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K8" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1165080658164273</v>
+        <v>0.120031602561992</v>
       </c>
       <c r="M8" t="n">
-        <v>3.893471935758455</v>
+        <v>3.90461735330631</v>
       </c>
       <c r="N8" t="n">
-        <v>26.10031034521446</v>
+        <v>26.13843570760081</v>
       </c>
       <c r="O8" t="n">
-        <v>5.108846283185124</v>
+        <v>5.112576230003891</v>
       </c>
       <c r="P8" t="n">
-        <v>392.6354324080547</v>
+        <v>392.6782380337926</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -38634,28 +38756,28 @@
         <v>0.0367</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1193908318393014</v>
+        <v>-0.1231048648132433</v>
       </c>
       <c r="J9" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K9" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03522443414875998</v>
+        <v>0.03743846877957568</v>
       </c>
       <c r="M9" t="n">
-        <v>3.467376389753466</v>
+        <v>3.473617777940009</v>
       </c>
       <c r="N9" t="n">
-        <v>20.71454770432206</v>
+        <v>20.75220359860698</v>
       </c>
       <c r="O9" t="n">
-        <v>4.551323730995419</v>
+        <v>4.555458659521232</v>
       </c>
       <c r="P9" t="n">
-        <v>392.4477226479884</v>
+        <v>392.4871107395098</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -38716,28 +38838,28 @@
         <v>0.0357</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05621625094150117</v>
+        <v>-0.05974464281104542</v>
       </c>
       <c r="J10" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K10" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01104961353666001</v>
+        <v>0.01247225551135323</v>
       </c>
       <c r="M10" t="n">
-        <v>3.024296294266076</v>
+        <v>3.028321120132458</v>
       </c>
       <c r="N10" t="n">
-        <v>15.00729440443899</v>
+        <v>15.05239511898695</v>
       </c>
       <c r="O10" t="n">
-        <v>3.873924935312891</v>
+        <v>3.879741630442284</v>
       </c>
       <c r="P10" t="n">
-        <v>393.034630839553</v>
+        <v>393.0720502670483</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -38798,28 +38920,28 @@
         <v>0.0406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07677208611986636</v>
+        <v>0.07321137895784831</v>
       </c>
       <c r="J11" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K11" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01793513595964746</v>
+        <v>0.01636015445162309</v>
       </c>
       <c r="M11" t="n">
-        <v>3.226456424905579</v>
+        <v>3.23113071983301</v>
       </c>
       <c r="N11" t="n">
-        <v>17.12353445174426</v>
+        <v>17.16363430949509</v>
       </c>
       <c r="O11" t="n">
-        <v>4.138059261507048</v>
+        <v>4.142901677507577</v>
       </c>
       <c r="P11" t="n">
-        <v>390.9211424640602</v>
+        <v>390.9589045805048</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -38880,28 +39002,28 @@
         <v>0.0457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06846307032712191</v>
+        <v>-0.0716059599522551</v>
       </c>
       <c r="J12" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K12" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01472782837799413</v>
+        <v>0.01612914358732209</v>
       </c>
       <c r="M12" t="n">
-        <v>3.240755919103185</v>
+        <v>3.243010169607006</v>
       </c>
       <c r="N12" t="n">
-        <v>16.63724736163899</v>
+        <v>16.65821626743338</v>
       </c>
       <c r="O12" t="n">
-        <v>4.078878198921731</v>
+        <v>4.081447815105981</v>
       </c>
       <c r="P12" t="n">
-        <v>390.3054048881808</v>
+        <v>390.3387358959914</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -38962,28 +39084,28 @@
         <v>0.0416</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09528066715674773</v>
+        <v>-0.09858038893433252</v>
       </c>
       <c r="J13" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K13" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03177320043031495</v>
+        <v>0.03398253274437779</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0304442212148</v>
+        <v>3.034289422112673</v>
       </c>
       <c r="N13" t="n">
-        <v>14.67834002787329</v>
+        <v>14.71342077337525</v>
       </c>
       <c r="O13" t="n">
-        <v>3.831232181410217</v>
+        <v>3.835807708081213</v>
       </c>
       <c r="P13" t="n">
-        <v>389.3945557289998</v>
+        <v>389.4295499745309</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -39044,28 +39166,28 @@
         <v>0.0362</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1140534384515466</v>
+        <v>-0.1176968942103632</v>
       </c>
       <c r="J14" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K14" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02481311787679152</v>
+        <v>0.02646751018505566</v>
       </c>
       <c r="M14" t="n">
-        <v>4.212030652753958</v>
+        <v>4.211709907378976</v>
       </c>
       <c r="N14" t="n">
-        <v>27.12529723414292</v>
+        <v>27.13755595416585</v>
       </c>
       <c r="O14" t="n">
-        <v>5.208195199312611</v>
+        <v>5.209371934712077</v>
       </c>
       <c r="P14" t="n">
-        <v>393.4913792999084</v>
+        <v>393.530018949483</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -39107,7 +39229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O611"/>
+  <dimension ref="A1:O613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86088,7 +86210,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>-36.68000070680074,174.74902295248305</t>
+          <t>-36.67999014572568,174.74904535578438</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -86154,6 +86276,160 @@
       <c r="O611" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>-36.68000275528465,174.74901860701442</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>-36.68068410215945,174.74937207756764</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>-36.6813977302427,174.74961575100878</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>-36.68209210770466,174.74988967820545</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>-36.682779733853344,174.75016476753711</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>-36.68344849970371,174.75045768974292</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>-36.684129403034675,174.75073207941264</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>-36.6848007336683,174.75105909980763</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>-36.685474774590915,174.75137651304522</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>-36.68614404110581,174.7516734348995</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>-36.6868067746588,174.75198476828785</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>-36.68746336182086,174.7523462119908</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>-36.68810316076602,174.7527594777036</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>-36.6800011620194,174.74902198682338</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>-36.6806813862352,174.7493787730447</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>-36.68139564139948,174.7496218218284</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>-36.68208851510923,174.7499039928756</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>-36.682777777430445,174.7501746558075</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>-36.68344476483916,174.7504721835625</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>-36.68412573134654,174.75074506553946</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>-36.68479616641346,174.7510752534062</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>-36.685471819288225,174.75138696545486</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>-36.686140371671094,174.75168486937872</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>-36.686802057884414,174.7519973471802</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>-36.6874582190482,174.75235940694157</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>-36.688098096477276,174.75277247129083</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0151/nzd0151.xlsx
+++ b/data/nzd0151/nzd0151.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O613"/>
+  <dimension ref="A1:O615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31715,6 +31715,108 @@
         <v>385.59</v>
       </c>
       <c r="O613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>394.32</v>
+      </c>
+      <c r="C614" t="n">
+        <v>383.97</v>
+      </c>
+      <c r="D614" t="n">
+        <v>373.65</v>
+      </c>
+      <c r="E614" t="n">
+        <v>366.73</v>
+      </c>
+      <c r="F614" t="n">
+        <v>376.35</v>
+      </c>
+      <c r="G614" t="n">
+        <v>381.99</v>
+      </c>
+      <c r="H614" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="I614" t="n">
+        <v>384.55</v>
+      </c>
+      <c r="J614" t="n">
+        <v>386.69</v>
+      </c>
+      <c r="K614" t="n">
+        <v>386.56</v>
+      </c>
+      <c r="L614" t="n">
+        <v>383.16</v>
+      </c>
+      <c r="M614" t="n">
+        <v>381.7</v>
+      </c>
+      <c r="N614" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>394.45</v>
+      </c>
+      <c r="C615" t="n">
+        <v>383.56</v>
+      </c>
+      <c r="D615" t="n">
+        <v>373.4</v>
+      </c>
+      <c r="E615" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="F615" t="n">
+        <v>376.35</v>
+      </c>
+      <c r="G615" t="n">
+        <v>381.99</v>
+      </c>
+      <c r="H615" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="I615" t="n">
+        <v>384.55</v>
+      </c>
+      <c r="J615" t="n">
+        <v>386.69</v>
+      </c>
+      <c r="K615" t="n">
+        <v>386.56</v>
+      </c>
+      <c r="L615" t="n">
+        <v>383.16</v>
+      </c>
+      <c r="M615" t="n">
+        <v>381.7</v>
+      </c>
+      <c r="N615" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="O615" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -31731,7 +31833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B628"/>
+  <dimension ref="A1:B630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38014,6 +38116,26 @@
       </c>
       <c r="B628" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -38182,28 +38304,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1991265084899545</v>
+        <v>-0.206751307196679</v>
       </c>
       <c r="J2" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K2" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05061455237079715</v>
+        <v>0.05414864426619015</v>
       </c>
       <c r="M2" t="n">
-        <v>5.080537097861868</v>
+        <v>5.103542300388219</v>
       </c>
       <c r="N2" t="n">
-        <v>39.61217537208392</v>
+        <v>39.92038994524142</v>
       </c>
       <c r="O2" t="n">
-        <v>6.293820411489664</v>
+        <v>6.318258458249505</v>
       </c>
       <c r="P2" t="n">
-        <v>411.2782920431013</v>
+        <v>411.3594296399119</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -38264,28 +38386,28 @@
         <v>0.0257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.222347003577582</v>
+        <v>-0.223942227493674</v>
       </c>
       <c r="J3" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K3" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05946683063610658</v>
+        <v>0.06064760324589202</v>
       </c>
       <c r="M3" t="n">
-        <v>5.301287393252552</v>
+        <v>5.292128451546087</v>
       </c>
       <c r="N3" t="n">
-        <v>41.64522865786561</v>
+        <v>41.52884343156163</v>
       </c>
       <c r="O3" t="n">
-        <v>6.453311449005511</v>
+        <v>6.444287658970666</v>
       </c>
       <c r="P3" t="n">
-        <v>392.0651777064397</v>
+        <v>392.0821536425063</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -38346,28 +38468,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2499881655245778</v>
+        <v>-0.2523508483205191</v>
       </c>
       <c r="J4" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K4" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09283361666333134</v>
+        <v>0.09492634472571371</v>
       </c>
       <c r="M4" t="n">
-        <v>4.690507842857882</v>
+        <v>4.68757065886902</v>
       </c>
       <c r="N4" t="n">
-        <v>32.52549708075304</v>
+        <v>32.46157946748323</v>
       </c>
       <c r="O4" t="n">
-        <v>5.703112928984752</v>
+        <v>5.697506425400785</v>
       </c>
       <c r="P4" t="n">
-        <v>383.7255735585837</v>
+        <v>383.7507160017612</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -38428,28 +38550,28 @@
         <v>0.0317</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2270252142103505</v>
+        <v>-0.2301512752523256</v>
       </c>
       <c r="J5" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K5" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08827629230368372</v>
+        <v>0.09087242697667097</v>
       </c>
       <c r="M5" t="n">
-        <v>4.358691133648885</v>
+        <v>4.363769381476318</v>
       </c>
       <c r="N5" t="n">
-        <v>28.35115246294549</v>
+        <v>28.33233820906268</v>
       </c>
       <c r="O5" t="n">
-        <v>5.324580026907802</v>
+        <v>5.322812997754353</v>
       </c>
       <c r="P5" t="n">
-        <v>377.5998308910513</v>
+        <v>377.6330959020657</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -38510,28 +38632,28 @@
         <v>0.0356</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2104976042526554</v>
+        <v>-0.2137811155822609</v>
       </c>
       <c r="J6" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K6" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0703193444750928</v>
+        <v>0.07267158446349764</v>
       </c>
       <c r="M6" t="n">
-        <v>4.414391151699925</v>
+        <v>4.419678021357328</v>
       </c>
       <c r="N6" t="n">
-        <v>31.20014848269736</v>
+        <v>31.17960149455958</v>
       </c>
       <c r="O6" t="n">
-        <v>5.585709308825278</v>
+        <v>5.583869759813491</v>
       </c>
       <c r="P6" t="n">
-        <v>386.9177199472888</v>
+        <v>386.9526607900971</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -38592,28 +38714,28 @@
         <v>0.0358</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2548030653285478</v>
+        <v>-0.2572104356289808</v>
       </c>
       <c r="J7" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K7" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1032206621761591</v>
+        <v>0.1055047080081819</v>
       </c>
       <c r="M7" t="n">
-        <v>4.209626821507888</v>
+        <v>4.211286153749559</v>
       </c>
       <c r="N7" t="n">
-        <v>30.04219180451723</v>
+        <v>29.98791924576893</v>
       </c>
       <c r="O7" t="n">
-        <v>5.481075788977674</v>
+        <v>5.47612264707146</v>
       </c>
       <c r="P7" t="n">
-        <v>392.3855570903647</v>
+        <v>392.4111746463321</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -38674,28 +38796,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2587333301638322</v>
+        <v>-0.2621104268808161</v>
       </c>
       <c r="J8" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K8" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.120031602561992</v>
+        <v>0.1232077945453723</v>
       </c>
       <c r="M8" t="n">
-        <v>3.90461735330631</v>
+        <v>3.91192306725528</v>
       </c>
       <c r="N8" t="n">
-        <v>26.13843570760081</v>
+        <v>26.13906421890951</v>
       </c>
       <c r="O8" t="n">
-        <v>5.112576230003891</v>
+        <v>5.112637696816537</v>
       </c>
       <c r="P8" t="n">
-        <v>392.6782380337926</v>
+        <v>392.7141747456386</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -38756,28 +38878,28 @@
         <v>0.0367</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1231048648132433</v>
+        <v>-0.1261766632390321</v>
       </c>
       <c r="J9" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K9" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03743846877957568</v>
+        <v>0.03939413660754776</v>
       </c>
       <c r="M9" t="n">
-        <v>3.473617777940009</v>
+        <v>3.476883930618023</v>
       </c>
       <c r="N9" t="n">
-        <v>20.75220359860698</v>
+        <v>20.75557009275532</v>
       </c>
       <c r="O9" t="n">
-        <v>4.555458659521232</v>
+        <v>4.555828145656431</v>
       </c>
       <c r="P9" t="n">
-        <v>392.4871107395098</v>
+        <v>392.5197986835951</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -38838,28 +38960,28 @@
         <v>0.0357</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05974464281104542</v>
+        <v>-0.06289286061057875</v>
       </c>
       <c r="J10" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K10" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01247225551135323</v>
+        <v>0.01383170591814897</v>
       </c>
       <c r="M10" t="n">
-        <v>3.028321120132458</v>
+        <v>3.030909908326315</v>
       </c>
       <c r="N10" t="n">
-        <v>15.05239511898695</v>
+        <v>15.07790246498589</v>
       </c>
       <c r="O10" t="n">
-        <v>3.879741630442284</v>
+        <v>3.883027487024253</v>
       </c>
       <c r="P10" t="n">
-        <v>393.0720502670483</v>
+        <v>393.1055514154157</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -38920,28 +39042,28 @@
         <v>0.0406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07321137895784831</v>
+        <v>0.06906763866905009</v>
       </c>
       <c r="J11" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K11" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01636015445162309</v>
+        <v>0.01458059204022877</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23113071983301</v>
+        <v>3.238570848281491</v>
       </c>
       <c r="N11" t="n">
-        <v>17.16363430949509</v>
+        <v>17.23685836141533</v>
       </c>
       <c r="O11" t="n">
-        <v>4.142901677507577</v>
+        <v>4.151729562654019</v>
       </c>
       <c r="P11" t="n">
-        <v>390.9589045805048</v>
+        <v>391.0029993936432</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -39002,28 +39124,28 @@
         <v>0.0457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0716059599522551</v>
+        <v>-0.07507059030455546</v>
       </c>
       <c r="J12" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K12" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01612914358732209</v>
+        <v>0.01772833144303732</v>
       </c>
       <c r="M12" t="n">
-        <v>3.243010169607006</v>
+        <v>3.246550995076002</v>
       </c>
       <c r="N12" t="n">
-        <v>16.65821626743338</v>
+        <v>16.69422877626126</v>
       </c>
       <c r="O12" t="n">
-        <v>4.081447815105981</v>
+        <v>4.085857165425788</v>
       </c>
       <c r="P12" t="n">
-        <v>390.3387358959914</v>
+        <v>390.3756040868825</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -39084,28 +39206,28 @@
         <v>0.0416</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09858038893433252</v>
+        <v>-0.1019391268122266</v>
       </c>
       <c r="J13" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K13" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03398253274437779</v>
+        <v>0.03629823879652028</v>
       </c>
       <c r="M13" t="n">
-        <v>3.034289422112673</v>
+        <v>3.038674299720887</v>
       </c>
       <c r="N13" t="n">
-        <v>14.71342077337525</v>
+        <v>14.75033423151762</v>
       </c>
       <c r="O13" t="n">
-        <v>3.835807708081213</v>
+        <v>3.840616386925102</v>
       </c>
       <c r="P13" t="n">
-        <v>389.4295499745309</v>
+        <v>389.465291330165</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -39166,28 +39288,28 @@
         <v>0.0362</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1176968942103632</v>
+        <v>-0.1209125774148692</v>
       </c>
       <c r="J14" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K14" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02646751018505566</v>
+        <v>0.02800711600241979</v>
       </c>
       <c r="M14" t="n">
-        <v>4.211709907378976</v>
+        <v>4.209976634400221</v>
       </c>
       <c r="N14" t="n">
-        <v>27.13755595416585</v>
+        <v>27.12692686356962</v>
       </c>
       <c r="O14" t="n">
-        <v>5.209371934712077</v>
+        <v>5.208351645537157</v>
       </c>
       <c r="P14" t="n">
-        <v>393.530018949483</v>
+        <v>393.5642380157962</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -39229,7 +39351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O613"/>
+  <dimension ref="A1:O615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86433,6 +86555,160 @@
         </is>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>-36.67999492552309,174.74903521635997</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>-36.680677981195316,174.74938716737347</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>-36.681392278007245,174.74963159687624</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>-36.6820878448487,174.7499066635229</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>-36.68277659497666,174.75018063223442</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>-36.68344374873601,174.75047612673373</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>-36.684124865663776,174.75074812730904</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>-36.68479577834597,174.7510766259341</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>-36.68547178943668,174.75138707103477</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>-36.68614540880393,174.75166917295695</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>-36.6868065464278,174.75198537694396</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>-36.68746143818851,174.75235114750694</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>-36.68809837128369,174.75277176621248</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>-36.679994333738684,174.74903647171735</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>-36.68067964317914,174.74938307014165</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>-36.681393163110535,174.7496290244953</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>-36.68208725501939,174.74990901369245</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-36.68277659497666,174.75018063223442</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>-36.68344374873601,174.75047612673373</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>-36.684124865663776,174.75074812730904</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>-36.68479577834597,174.7510766259341</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>-36.68547178943668,174.75138707103477</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>-36.68614540880393,174.75166917295695</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>-36.6868065464278,174.75198537694396</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>-36.68746143818851,174.75235114750694</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>-36.68809837128369,174.75277176621248</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0151/nzd0151.xlsx
+++ b/data/nzd0151/nzd0151.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O615"/>
+  <dimension ref="A1:O617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31819,6 +31819,108 @@
       <c r="O615" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>396.83</v>
+      </c>
+      <c r="C616" t="n">
+        <v>385.04</v>
+      </c>
+      <c r="D616" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="E616" t="n">
+        <v>371.83</v>
+      </c>
+      <c r="F616" t="n">
+        <v>380.94</v>
+      </c>
+      <c r="G616" t="n">
+        <v>386.13</v>
+      </c>
+      <c r="H616" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="I616" t="n">
+        <v>388</v>
+      </c>
+      <c r="J616" t="n">
+        <v>388.01</v>
+      </c>
+      <c r="K616" t="n">
+        <v>387.19</v>
+      </c>
+      <c r="L616" t="n">
+        <v>383.25</v>
+      </c>
+      <c r="M616" t="n">
+        <v>383.52</v>
+      </c>
+      <c r="N616" t="n">
+        <v>386.65</v>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>395.6</v>
+      </c>
+      <c r="C617" t="n">
+        <v>384.39</v>
+      </c>
+      <c r="D617" t="n">
+        <v>377.99</v>
+      </c>
+      <c r="E617" t="n">
+        <v>371.45</v>
+      </c>
+      <c r="F617" t="n">
+        <v>380.84</v>
+      </c>
+      <c r="G617" t="n">
+        <v>385.98</v>
+      </c>
+      <c r="H617" t="n">
+        <v>383.99</v>
+      </c>
+      <c r="I617" t="n">
+        <v>387.93</v>
+      </c>
+      <c r="J617" t="n">
+        <v>388.19</v>
+      </c>
+      <c r="K617" t="n">
+        <v>387.19</v>
+      </c>
+      <c r="L617" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="M617" t="n">
+        <v>383.79</v>
+      </c>
+      <c r="N617" t="n">
+        <v>386.79</v>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31833,7 +31935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B630"/>
+  <dimension ref="A1:B632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38136,6 +38238,26 @@
       </c>
       <c r="B630" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -38304,34 +38426,30 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.206751307196679</v>
+        <v>-0.2130814014037029</v>
       </c>
       <c r="J2" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K2" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05414864426619015</v>
+        <v>0.05729937767235338</v>
       </c>
       <c r="M2" t="n">
-        <v>5.103542300388219</v>
+        <v>5.119601301765308</v>
       </c>
       <c r="N2" t="n">
-        <v>39.92038994524142</v>
+        <v>40.09245526188805</v>
       </c>
       <c r="O2" t="n">
-        <v>6.318258458249505</v>
+        <v>6.331860331836769</v>
       </c>
       <c r="P2" t="n">
-        <v>411.3594296399119</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>411.4271098182444</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.7452273375528 -36.68178988531498, 174.75411870463546 -36.67759835244193)</t>
@@ -38386,34 +38504,30 @@
         <v>0.0257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.223942227493674</v>
+        <v>-0.2248848388902646</v>
       </c>
       <c r="J3" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K3" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06064760324589202</v>
+        <v>0.06152874749701176</v>
       </c>
       <c r="M3" t="n">
-        <v>5.292128451546087</v>
+        <v>5.279669798253892</v>
       </c>
       <c r="N3" t="n">
-        <v>41.52884343156163</v>
+        <v>41.40100941908428</v>
       </c>
       <c r="O3" t="n">
-        <v>6.444287658970666</v>
+        <v>6.434361617059169</v>
       </c>
       <c r="P3" t="n">
-        <v>392.0821536425063</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>392.0922326303594</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.7455499806671 -36.68223438937886, 174.7547520215089 -36.678501624137525)</t>
@@ -38468,34 +38582,30 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2523508483205191</v>
+        <v>-0.2516498171781168</v>
       </c>
       <c r="J4" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K4" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09492634472571371</v>
+        <v>0.09505110341362366</v>
       </c>
       <c r="M4" t="n">
-        <v>4.68757065886902</v>
+        <v>4.675620899356607</v>
       </c>
       <c r="N4" t="n">
-        <v>32.46157946748323</v>
+        <v>32.3599473441393</v>
       </c>
       <c r="O4" t="n">
-        <v>5.697506425400785</v>
+        <v>5.688580433125588</v>
       </c>
       <c r="P4" t="n">
-        <v>383.7507160017612</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>383.7432214332766</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.74578684843877 -36.68271509294474, 174.7552623577399 -36.67945466916763)</t>
@@ -38550,34 +38660,30 @@
         <v>0.0317</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2301512752523256</v>
+        <v>-0.230085854373393</v>
       </c>
       <c r="J5" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K5" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09087242697667097</v>
+        <v>0.09141561424891131</v>
       </c>
       <c r="M5" t="n">
-        <v>4.363769381476318</v>
+        <v>4.350145577827281</v>
       </c>
       <c r="N5" t="n">
-        <v>28.33233820906268</v>
+        <v>28.24050128536248</v>
       </c>
       <c r="O5" t="n">
-        <v>5.322812997754353</v>
+        <v>5.314179267333995</v>
       </c>
       <c r="P5" t="n">
-        <v>377.6330959020657</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>377.6323970840533</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.74598898539622 -36.68307100022963, 174.75582741129088 -36.68060172216417)</t>
@@ -38632,34 +38738,30 @@
         <v>0.0356</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2137811155822609</v>
+        <v>-0.2140467969229969</v>
       </c>
       <c r="J6" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K6" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07267158446349764</v>
+        <v>0.07332105833507596</v>
       </c>
       <c r="M6" t="n">
-        <v>4.419678021357328</v>
+        <v>4.406905994481375</v>
       </c>
       <c r="N6" t="n">
-        <v>31.17960149455958</v>
+        <v>31.07890516663332</v>
       </c>
       <c r="O6" t="n">
-        <v>5.583869759813491</v>
+        <v>5.574845752721175</v>
       </c>
       <c r="P6" t="n">
-        <v>386.9526607900971</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>386.9555014724056</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.7460910807978 -36.68358564677986, 174.75609909041776 -36.68160544652905)</t>
@@ -38714,34 +38816,30 @@
         <v>0.0358</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2572104356289808</v>
+        <v>-0.2569159882452162</v>
       </c>
       <c r="J7" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K7" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1055047080081819</v>
+        <v>0.1059602733632325</v>
       </c>
       <c r="M7" t="n">
-        <v>4.211286153749559</v>
+        <v>4.198645431924457</v>
       </c>
       <c r="N7" t="n">
-        <v>29.98791924576893</v>
+        <v>29.89122313688248</v>
       </c>
       <c r="O7" t="n">
-        <v>5.47612264707146</v>
+        <v>5.467286633868987</v>
       </c>
       <c r="P7" t="n">
-        <v>392.4111746463321</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>392.4080268002858</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.74640511761024 -36.68449271093772, 174.7562200633887 -36.681963446450574)</t>
@@ -38796,34 +38894,30 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2621104268808161</v>
+        <v>-0.2633437208562948</v>
       </c>
       <c r="J8" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K8" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1232077945453723</v>
+        <v>0.1249555089057557</v>
       </c>
       <c r="M8" t="n">
-        <v>3.91192306725528</v>
+        <v>3.906439061653638</v>
       </c>
       <c r="N8" t="n">
-        <v>26.13906421890951</v>
+        <v>26.06563672779461</v>
       </c>
       <c r="O8" t="n">
-        <v>5.112637696816537</v>
+        <v>5.105451667364466</v>
       </c>
       <c r="P8" t="n">
-        <v>392.7141747456386</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>392.7273601782883</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.7467287013772 -36.68526123182616, 174.75645183048127 -36.68251203537312)</t>
@@ -38878,34 +38972,30 @@
         <v>0.0367</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1261766632390321</v>
+        <v>-0.1269710415378434</v>
       </c>
       <c r="J9" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K9" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03939413660754776</v>
+        <v>0.04013696906696784</v>
       </c>
       <c r="M9" t="n">
-        <v>3.476883930618023</v>
+        <v>3.469310673904686</v>
       </c>
       <c r="N9" t="n">
-        <v>20.75557009275532</v>
+        <v>20.69291774431642</v>
       </c>
       <c r="O9" t="n">
-        <v>4.555828145656431</v>
+        <v>4.548946882995715</v>
       </c>
       <c r="P9" t="n">
-        <v>392.5197986835951</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>392.528291886019</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (174.74701652001593 -36.685943644133175, 174.75673969688296 -36.683194439481646)</t>
@@ -38960,34 +39050,30 @@
         <v>0.0357</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06289286061057875</v>
+        <v>-0.06508008929958384</v>
       </c>
       <c r="J10" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K10" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01383170591814897</v>
+        <v>0.0148653336051574</v>
       </c>
       <c r="M10" t="n">
-        <v>3.030909908326315</v>
+        <v>3.029911707031048</v>
       </c>
       <c r="N10" t="n">
-        <v>15.07790246498589</v>
+        <v>15.06485299355902</v>
       </c>
       <c r="O10" t="n">
-        <v>3.883027487024253</v>
+        <v>3.881346801505764</v>
       </c>
       <c r="P10" t="n">
-        <v>393.1055514154157</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>393.1289358692072</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (174.7473043386543 -36.6866260503853, 174.75702756328542 -36.683876837535394)</t>
@@ -39042,34 +39128,30 @@
         <v>0.0406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06906763866905009</v>
+        <v>0.06537610364336789</v>
       </c>
       <c r="J11" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K11" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01458059204022877</v>
+        <v>0.01309899161602823</v>
       </c>
       <c r="M11" t="n">
-        <v>3.238570848281491</v>
+        <v>3.244680015782849</v>
       </c>
       <c r="N11" t="n">
-        <v>17.23685836141533</v>
+        <v>17.28309317369268</v>
       </c>
       <c r="O11" t="n">
-        <v>4.151729562654019</v>
+        <v>4.157293972488917</v>
       </c>
       <c r="P11" t="n">
-        <v>391.0029993936432</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>391.0424674340981</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>LINESTRING (174.7476508192542 -36.68743484836185, 174.75722350081196 -36.68436280294616)</t>
@@ -39124,34 +39206,30 @@
         <v>0.0457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07507059030455546</v>
+        <v>-0.07807748088541389</v>
       </c>
       <c r="J12" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K12" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01772833144303732</v>
+        <v>0.01920576774431004</v>
       </c>
       <c r="M12" t="n">
-        <v>3.246550995076002</v>
+        <v>3.248071509385962</v>
       </c>
       <c r="N12" t="n">
-        <v>16.69422877626126</v>
+        <v>16.70880889072364</v>
       </c>
       <c r="O12" t="n">
-        <v>4.085857165425788</v>
+        <v>4.087640993375475</v>
       </c>
       <c r="P12" t="n">
-        <v>390.3756040868825</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>390.4077504562956</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>LINESTRING (174.74809842355305 -36.68826396783249, 174.75743961295373 -36.68476116564556)</t>
@@ -39206,34 +39284,30 @@
         <v>0.0416</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1019391268122266</v>
+        <v>-0.1039738002898456</v>
       </c>
       <c r="J13" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K13" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03629823879652028</v>
+        <v>0.0378890039362183</v>
       </c>
       <c r="M13" t="n">
-        <v>3.038674299720887</v>
+        <v>3.037483603289791</v>
       </c>
       <c r="N13" t="n">
-        <v>14.75033423151762</v>
+        <v>14.73355340525196</v>
       </c>
       <c r="O13" t="n">
-        <v>3.840616386925102</v>
+        <v>3.838431112479675</v>
       </c>
       <c r="P13" t="n">
-        <v>389.465291330165</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>389.4870445851639</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>LINESTRING (174.74850640466582 -36.68895984831127, 174.75778129899888 -36.6853448402087)</t>
@@ -39288,34 +39362,30 @@
         <v>0.0362</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1209125774148692</v>
+        <v>-0.1232960738026336</v>
       </c>
       <c r="J14" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K14" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02800711600241979</v>
+        <v>0.02924708145319699</v>
       </c>
       <c r="M14" t="n">
-        <v>4.209976634400221</v>
+        <v>4.205101406575071</v>
       </c>
       <c r="N14" t="n">
-        <v>27.12692686356962</v>
+        <v>27.08147662355336</v>
       </c>
       <c r="O14" t="n">
-        <v>5.208351645537157</v>
+        <v>5.203986608702348</v>
       </c>
       <c r="P14" t="n">
-        <v>393.5642380157962</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>393.5897209150531</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>LINESTRING (174.74888851952352 -36.68961178637735, 174.7581634512747 -36.68599676853558)</t>
@@ -39351,7 +39421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O615"/>
+  <dimension ref="A1:O617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86709,6 +86779,160 @@
         </is>
       </c>
     </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>-36.679983499529804,174.74905945441043</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>-36.68067364382226,174.7493978601483</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>-36.681375815075995,174.7496794431503</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>-36.68207417152111,174.7499611447165</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>-36.68276672685076,174.75023050822597</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-36.6834323793569,174.75052024761533</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>-36.68411561180865,174.75078085656529</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>-36.684785479625816,174.7511130507075</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>-36.685467849031696,174.75140100757966</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>-36.68614330721895,174.75167572179544</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>-36.686806204081314,174.75198628992814</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>-36.687454293266576,174.75236947942187</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>-36.688093935122716,174.75278314819062</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>-36.67998909872233,174.74904757680096</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>-36.68067627867517,174.7493913645376</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>-36.681376912605316,174.74967625339937</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>-36.68207519031891,174.74995708533416</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>-36.68276694184282,174.7502294216032</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>-36.68343279129121,174.7505186490329</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>-36.6841150446366,174.7507828625517</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>-36.68478568858546,174.75111231165423</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>-36.68546731170362,174.7514029080175</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>-36.68614330721895,174.75167572179544</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>-36.686802057884414,174.7519973471802</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>-36.687453233305405,174.75237219899137</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>-36.68809338550978,174.75278455834712</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0151/nzd0151.xlsx
+++ b/data/nzd0151/nzd0151.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O617"/>
+  <dimension ref="A1:O620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31919,6 +31919,159 @@
         <v>386.79</v>
       </c>
       <c r="O617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>399.11</v>
+      </c>
+      <c r="C618" t="n">
+        <v>386.19</v>
+      </c>
+      <c r="D618" t="n">
+        <v>380.14</v>
+      </c>
+      <c r="E618" t="n">
+        <v>373.05</v>
+      </c>
+      <c r="F618" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="G618" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="H618" t="n">
+        <v>385.46</v>
+      </c>
+      <c r="I618" t="n">
+        <v>389.36</v>
+      </c>
+      <c r="J618" t="n">
+        <v>389.55</v>
+      </c>
+      <c r="K618" t="n">
+        <v>388.51</v>
+      </c>
+      <c r="L618" t="n">
+        <v>385.32</v>
+      </c>
+      <c r="M618" t="n">
+        <v>384.65</v>
+      </c>
+      <c r="N618" t="n">
+        <v>387.31</v>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>401.06</v>
+      </c>
+      <c r="C619" t="n">
+        <v>385.4</v>
+      </c>
+      <c r="D619" t="n">
+        <v>378.17</v>
+      </c>
+      <c r="E619" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="F619" t="n">
+        <v>382.23</v>
+      </c>
+      <c r="G619" t="n">
+        <v>386.09</v>
+      </c>
+      <c r="H619" t="n">
+        <v>385.38</v>
+      </c>
+      <c r="I619" t="n">
+        <v>389.16</v>
+      </c>
+      <c r="J619" t="n">
+        <v>390.31</v>
+      </c>
+      <c r="K619" t="n">
+        <v>388.19</v>
+      </c>
+      <c r="L619" t="n">
+        <v>385.12</v>
+      </c>
+      <c r="M619" t="n">
+        <v>384.58</v>
+      </c>
+      <c r="N619" t="n">
+        <v>387.7</v>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>400.89</v>
+      </c>
+      <c r="C620" t="n">
+        <v>386.16</v>
+      </c>
+      <c r="D620" t="n">
+        <v>378.42</v>
+      </c>
+      <c r="E620" t="n">
+        <v>373.26</v>
+      </c>
+      <c r="F620" t="n">
+        <v>383.22</v>
+      </c>
+      <c r="G620" t="n">
+        <v>387.31</v>
+      </c>
+      <c r="H620" t="n">
+        <v>386.32</v>
+      </c>
+      <c r="I620" t="n">
+        <v>389.9</v>
+      </c>
+      <c r="J620" t="n">
+        <v>390.47</v>
+      </c>
+      <c r="K620" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="L620" t="n">
+        <v>387.96</v>
+      </c>
+      <c r="M620" t="n">
+        <v>387.05</v>
+      </c>
+      <c r="N620" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="O620" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31935,7 +32088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B632"/>
+  <dimension ref="A1:B635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38258,6 +38411,36 @@
       </c>
       <c r="B632" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -38426,28 +38609,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2130814014037029</v>
+        <v>-0.2183500192138233</v>
       </c>
       <c r="J2" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K2" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05729937767235338</v>
+        <v>0.06039472490236453</v>
       </c>
       <c r="M2" t="n">
-        <v>5.119601301765308</v>
+        <v>5.121938506820644</v>
       </c>
       <c r="N2" t="n">
-        <v>40.09245526188805</v>
+        <v>40.04201463779299</v>
       </c>
       <c r="O2" t="n">
-        <v>6.331860331836769</v>
+        <v>6.327875997346423</v>
       </c>
       <c r="P2" t="n">
-        <v>411.4271098182444</v>
+        <v>411.4835938369646</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38504,28 +38687,28 @@
         <v>0.0257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2248848388902646</v>
+        <v>-0.2250847029315682</v>
       </c>
       <c r="J3" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K3" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06152874749701176</v>
+        <v>0.06224901003009864</v>
       </c>
       <c r="M3" t="n">
-        <v>5.279669798253892</v>
+        <v>5.255449157160147</v>
       </c>
       <c r="N3" t="n">
-        <v>41.40100941908428</v>
+        <v>41.20121809360734</v>
       </c>
       <c r="O3" t="n">
-        <v>6.434361617059169</v>
+        <v>6.418817499633974</v>
       </c>
       <c r="P3" t="n">
-        <v>392.0922326303594</v>
+        <v>392.0943764241126</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38582,28 +38765,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2516498171781168</v>
+        <v>-0.2498549509870002</v>
       </c>
       <c r="J4" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K4" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09505110341362366</v>
+        <v>0.09468313996965005</v>
       </c>
       <c r="M4" t="n">
-        <v>4.675620899356607</v>
+        <v>4.661254602005754</v>
       </c>
       <c r="N4" t="n">
-        <v>32.3599473441393</v>
+        <v>32.22306800761443</v>
       </c>
       <c r="O4" t="n">
-        <v>5.688580433125588</v>
+        <v>5.67653662082915</v>
       </c>
       <c r="P4" t="n">
-        <v>383.7432214332766</v>
+        <v>383.7239849444296</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38660,28 +38843,28 @@
         <v>0.0317</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.230085854373393</v>
+        <v>-0.2288675081759437</v>
       </c>
       <c r="J5" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K5" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09141561424891131</v>
+        <v>0.09139185892871082</v>
       </c>
       <c r="M5" t="n">
-        <v>4.350145577827281</v>
+        <v>4.333615832824407</v>
       </c>
       <c r="N5" t="n">
-        <v>28.24050128536248</v>
+        <v>28.11256077355124</v>
       </c>
       <c r="O5" t="n">
-        <v>5.314179267333995</v>
+        <v>5.302127947678295</v>
       </c>
       <c r="P5" t="n">
-        <v>377.6323970840533</v>
+        <v>377.6193329850097</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38738,28 +38921,28 @@
         <v>0.0356</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2140467969229969</v>
+        <v>-0.2126722122472522</v>
       </c>
       <c r="J6" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K6" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07332105833507596</v>
+        <v>0.07314669694355191</v>
       </c>
       <c r="M6" t="n">
-        <v>4.406905994481375</v>
+        <v>4.390955787867708</v>
       </c>
       <c r="N6" t="n">
-        <v>31.07890516663332</v>
+        <v>30.93860956973173</v>
       </c>
       <c r="O6" t="n">
-        <v>5.574845752721175</v>
+        <v>5.56224860732885</v>
       </c>
       <c r="P6" t="n">
-        <v>386.9555014724056</v>
+        <v>386.9407597715289</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38816,28 +38999,28 @@
         <v>0.0358</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2569159882452162</v>
+        <v>-0.2557059614966199</v>
       </c>
       <c r="J7" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K7" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1059602733632325</v>
+        <v>0.106046915922419</v>
       </c>
       <c r="M7" t="n">
-        <v>4.198645431924457</v>
+        <v>4.182486110311086</v>
       </c>
       <c r="N7" t="n">
-        <v>29.89122313688248</v>
+        <v>29.75509922585859</v>
       </c>
       <c r="O7" t="n">
-        <v>5.467286633868987</v>
+        <v>5.454823482557304</v>
       </c>
       <c r="P7" t="n">
-        <v>392.4080268002858</v>
+        <v>392.3950518489423</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38894,28 +39077,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2633437208562948</v>
+        <v>-0.2633611259001178</v>
       </c>
       <c r="J8" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K8" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1249555089057557</v>
+        <v>0.1261353841946338</v>
       </c>
       <c r="M8" t="n">
-        <v>3.906439061653638</v>
+        <v>3.889521773270055</v>
       </c>
       <c r="N8" t="n">
-        <v>26.06563672779461</v>
+        <v>25.94021507966213</v>
       </c>
       <c r="O8" t="n">
-        <v>5.105451667364466</v>
+        <v>5.093153745928168</v>
       </c>
       <c r="P8" t="n">
-        <v>392.7273601782883</v>
+        <v>392.7275429162489</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38972,28 +39155,28 @@
         <v>0.0367</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1269710415378434</v>
+        <v>-0.126662561488527</v>
       </c>
       <c r="J9" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K9" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04013696906696784</v>
+        <v>0.0403586260492359</v>
       </c>
       <c r="M9" t="n">
-        <v>3.469310673904686</v>
+        <v>3.454109963032637</v>
       </c>
       <c r="N9" t="n">
-        <v>20.69291774431642</v>
+        <v>20.59359351203968</v>
       </c>
       <c r="O9" t="n">
-        <v>4.548946882995715</v>
+        <v>4.538016473310743</v>
       </c>
       <c r="P9" t="n">
-        <v>392.528291886019</v>
+        <v>392.5249818518687</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39050,28 +39233,28 @@
         <v>0.0357</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06508008929958384</v>
+        <v>-0.06633216969874417</v>
       </c>
       <c r="J10" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K10" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0148653336051574</v>
+        <v>0.01558768251282838</v>
       </c>
       <c r="M10" t="n">
-        <v>3.029911707031048</v>
+        <v>3.020344805138307</v>
       </c>
       <c r="N10" t="n">
-        <v>15.06485299355902</v>
+        <v>15.00054043831392</v>
       </c>
       <c r="O10" t="n">
-        <v>3.881346801505764</v>
+        <v>3.873053115865302</v>
       </c>
       <c r="P10" t="n">
-        <v>393.1289358692072</v>
+        <v>393.1423567600804</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39128,28 +39311,28 @@
         <v>0.0406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06537610364336789</v>
+        <v>0.06155724762672007</v>
       </c>
       <c r="J11" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K11" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01309899161602823</v>
+        <v>0.01170255632358785</v>
       </c>
       <c r="M11" t="n">
-        <v>3.244680015782849</v>
+        <v>3.246122817193402</v>
       </c>
       <c r="N11" t="n">
-        <v>17.28309317369268</v>
+        <v>17.27540869985656</v>
       </c>
       <c r="O11" t="n">
-        <v>4.157293972488917</v>
+        <v>4.15636965389949</v>
       </c>
       <c r="P11" t="n">
-        <v>391.0424674340981</v>
+        <v>391.0834100078119</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39206,28 +39389,28 @@
         <v>0.0457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07807748088541389</v>
+        <v>-0.08021883879956937</v>
       </c>
       <c r="J12" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K12" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01920576774431004</v>
+        <v>0.02042681888572584</v>
       </c>
       <c r="M12" t="n">
-        <v>3.248071509385962</v>
+        <v>3.240824841172069</v>
       </c>
       <c r="N12" t="n">
-        <v>16.70880889072364</v>
+        <v>16.65911409488211</v>
       </c>
       <c r="O12" t="n">
-        <v>4.087640993375475</v>
+        <v>4.081557802467351</v>
       </c>
       <c r="P12" t="n">
-        <v>390.4077504562956</v>
+        <v>390.4306998399755</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -39284,28 +39467,28 @@
         <v>0.0416</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1039738002898456</v>
+        <v>-0.1052374902737029</v>
       </c>
       <c r="J13" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K13" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0378890039362183</v>
+        <v>0.03914141350492339</v>
       </c>
       <c r="M13" t="n">
-        <v>3.037483603289791</v>
+        <v>3.029216143950251</v>
       </c>
       <c r="N13" t="n">
-        <v>14.73355340525196</v>
+        <v>14.67665032786185</v>
       </c>
       <c r="O13" t="n">
-        <v>3.838431112479675</v>
+        <v>3.831011658539014</v>
       </c>
       <c r="P13" t="n">
-        <v>389.4870445851639</v>
+        <v>389.5005839461288</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -39362,28 +39545,28 @@
         <v>0.0362</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1232960738026336</v>
+        <v>-0.1252143254989395</v>
       </c>
       <c r="J14" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K14" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02924708145319699</v>
+        <v>0.03042146481744556</v>
       </c>
       <c r="M14" t="n">
-        <v>4.205101406575071</v>
+        <v>4.191723542172005</v>
       </c>
       <c r="N14" t="n">
-        <v>27.08147662355336</v>
+        <v>26.97577431459186</v>
       </c>
       <c r="O14" t="n">
-        <v>5.203986608702348</v>
+        <v>5.193820781909197</v>
       </c>
       <c r="P14" t="n">
-        <v>393.5897209150531</v>
+        <v>393.6102771928713</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -39421,7 +39604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O617"/>
+  <dimension ref="A1:O620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86933,6 +87116,237 @@
         </is>
       </c>
     </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>-36.67997312053577,174.74908147143793</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>-36.68066898215857,174.74940935238155</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>-36.681369300706635,174.74969837586372</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>-36.68207090064304,174.74997417746962</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>-36.68276313648176,174.75024865482519</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>-36.683429715514556,174.7505305851146</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>-36.68411065651486,174.75079838255076</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>-36.68478141983748,174.75112740945596</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>-36.685463251890525,174.7514172668802</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>-36.68613890389689,174.7516894431701</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>-36.6867983301102,174.75200728856177</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>-36.687449857132364,174.75238086132333</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>-36.688091344090175,174.75278979607103</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>-36.679964243761425,174.74910030178566</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>-36.68067218451896,174.7494014577171</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>-36.68137627533024,174.74967810551286</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>-36.68207366212216,174.74996317440764</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>-36.68276395345218,174.75024452565904</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>-36.68343248920604,174.7505198213267</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>-36.68411089532426,174.75079753792502</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>-36.684782016865285,174.7511252978754</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>-36.68546098317071,174.7514252909498</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>-36.68613997136904,174.75168611677637</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>-36.68679909088052,174.75200525970848</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>-36.68745013193717,174.75238015624984</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>-36.68808981302531,174.75279372436378</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>-36.67996501763417,174.7490986601658</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>-36.68066910376721,174.74940905258416</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>-36.6813753902259,174.74968067789263</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>-36.68207033762291,174.74997642081226</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>-36.68276182502893,174.75025528322325</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>-36.68342913880629,174.75053282312982</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>-36.684108089313476,174.75080746227724</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>-36.68477980786223,174.7511331107233</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>-36.685460505545414,174.75142698022756</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>-36.68613443385627,174.75170337244268</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>-36.68678828793892,174.75203406942148</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>-36.68744043525085,174.75240503526888</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>-36.68808070514969,174.75281709266613</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0151/nzd0151.xlsx
+++ b/data/nzd0151/nzd0151.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O620"/>
+  <dimension ref="A1:O621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32072,6 +32072,57 @@
         <v>390.02</v>
       </c>
       <c r="O620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="C621" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="D621" t="n">
+        <v>379.07</v>
+      </c>
+      <c r="E621" t="n">
+        <v>374</v>
+      </c>
+      <c r="F621" t="n">
+        <v>384.36</v>
+      </c>
+      <c r="G621" t="n">
+        <v>388.51</v>
+      </c>
+      <c r="H621" t="n">
+        <v>387.99</v>
+      </c>
+      <c r="I621" t="n">
+        <v>391.66</v>
+      </c>
+      <c r="J621" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="K621" t="n">
+        <v>390.38</v>
+      </c>
+      <c r="L621" t="n">
+        <v>388.17</v>
+      </c>
+      <c r="M621" t="n">
+        <v>386.31</v>
+      </c>
+      <c r="N621" t="n">
+        <v>388.56</v>
+      </c>
+      <c r="O621" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32088,7 +32139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B635"/>
+  <dimension ref="A1:B636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38441,6 +38492,16 @@
       </c>
       <c r="B635" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>-0.85</v>
       </c>
     </row>
   </sheetData>
@@ -38609,28 +38670,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2183500192138233</v>
+        <v>-0.2204228376421573</v>
       </c>
       <c r="J2" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K2" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06039472490236453</v>
+        <v>0.0615877475689437</v>
       </c>
       <c r="M2" t="n">
-        <v>5.121938506820644</v>
+        <v>5.124366779691348</v>
       </c>
       <c r="N2" t="n">
-        <v>40.04201463779299</v>
+        <v>40.04254777130707</v>
       </c>
       <c r="O2" t="n">
-        <v>6.327875997346423</v>
+        <v>6.327918122993302</v>
       </c>
       <c r="P2" t="n">
-        <v>411.4835938369646</v>
+        <v>411.5059079417449</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38687,28 +38748,28 @@
         <v>0.0257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2250847029315682</v>
+        <v>-0.225248987599705</v>
       </c>
       <c r="J3" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K3" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06224901003009864</v>
+        <v>0.06254221485854716</v>
       </c>
       <c r="M3" t="n">
-        <v>5.255449157160147</v>
+        <v>5.24779434571303</v>
       </c>
       <c r="N3" t="n">
-        <v>41.20121809360734</v>
+        <v>41.13517355635635</v>
       </c>
       <c r="O3" t="n">
-        <v>6.418817499633974</v>
+        <v>6.413670833177857</v>
       </c>
       <c r="P3" t="n">
-        <v>392.0943764241126</v>
+        <v>392.0961449655576</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38765,28 +38826,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2498549509870002</v>
+        <v>-0.2492029882412534</v>
       </c>
       <c r="J4" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K4" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09468313996965005</v>
+        <v>0.09452355015125458</v>
       </c>
       <c r="M4" t="n">
-        <v>4.661254602005754</v>
+        <v>4.656744067737833</v>
       </c>
       <c r="N4" t="n">
-        <v>32.22306800761443</v>
+        <v>32.17753727113275</v>
       </c>
       <c r="O4" t="n">
-        <v>5.67653662082915</v>
+        <v>5.672524770429192</v>
       </c>
       <c r="P4" t="n">
-        <v>383.7239849444296</v>
+        <v>383.7169664980367</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38843,28 +38904,28 @@
         <v>0.0317</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2288675081759437</v>
+        <v>-0.2280612693258778</v>
       </c>
       <c r="J5" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K5" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09139185892871082</v>
+        <v>0.09107296891084504</v>
       </c>
       <c r="M5" t="n">
-        <v>4.333615832824407</v>
+        <v>4.329606287211117</v>
       </c>
       <c r="N5" t="n">
-        <v>28.11256077355124</v>
+        <v>28.07706936850662</v>
       </c>
       <c r="O5" t="n">
-        <v>5.302127947678295</v>
+        <v>5.2987799886867</v>
       </c>
       <c r="P5" t="n">
-        <v>377.6193329850097</v>
+        <v>377.6106537403965</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38921,28 +38982,28 @@
         <v>0.0356</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2126722122472522</v>
+        <v>-0.2116688918128711</v>
       </c>
       <c r="J6" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K6" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07314669694355191</v>
+        <v>0.07271473161183672</v>
       </c>
       <c r="M6" t="n">
-        <v>4.390955787867708</v>
+        <v>4.387792499100928</v>
       </c>
       <c r="N6" t="n">
-        <v>30.93860956973173</v>
+        <v>30.90396496187532</v>
       </c>
       <c r="O6" t="n">
-        <v>5.56224860732885</v>
+        <v>5.559133472212673</v>
       </c>
       <c r="P6" t="n">
-        <v>386.9407597715289</v>
+        <v>386.9299589232757</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38999,28 +39060,28 @@
         <v>0.0358</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2557059614966199</v>
+        <v>-0.2547543679437022</v>
       </c>
       <c r="J7" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K7" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L7" t="n">
-        <v>0.106046915922419</v>
+        <v>0.105634666068243</v>
       </c>
       <c r="M7" t="n">
-        <v>4.182486110311086</v>
+        <v>4.179013778244697</v>
       </c>
       <c r="N7" t="n">
-        <v>29.75509922585859</v>
+        <v>29.72083095090037</v>
       </c>
       <c r="O7" t="n">
-        <v>5.454823482557304</v>
+        <v>5.451681479222752</v>
       </c>
       <c r="P7" t="n">
-        <v>392.3950518489423</v>
+        <v>392.3848078459183</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39077,28 +39138,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2633611259001178</v>
+        <v>-0.262619714170868</v>
       </c>
       <c r="J8" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K8" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1261353841946338</v>
+        <v>0.1258713695742206</v>
       </c>
       <c r="M8" t="n">
-        <v>3.889521773270055</v>
+        <v>3.886275842756619</v>
       </c>
       <c r="N8" t="n">
-        <v>25.94021507966213</v>
+        <v>25.90670690452206</v>
       </c>
       <c r="O8" t="n">
-        <v>5.093153745928168</v>
+        <v>5.089863151846232</v>
       </c>
       <c r="P8" t="n">
-        <v>392.7275429162489</v>
+        <v>392.7195615422965</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39155,28 +39216,28 @@
         <v>0.0367</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.126662561488527</v>
+        <v>-0.1258457400745759</v>
       </c>
       <c r="J9" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K9" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0403586260492359</v>
+        <v>0.03997815053564113</v>
       </c>
       <c r="M9" t="n">
-        <v>3.454109963032637</v>
+        <v>3.452780388977894</v>
       </c>
       <c r="N9" t="n">
-        <v>20.59359351203968</v>
+        <v>20.57048978758659</v>
       </c>
       <c r="O9" t="n">
-        <v>4.538016473310743</v>
+        <v>4.535470183739123</v>
       </c>
       <c r="P9" t="n">
-        <v>392.5249818518687</v>
+        <v>392.5161886848607</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39233,28 +39294,28 @@
         <v>0.0357</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06633216969874417</v>
+        <v>-0.06638785327333588</v>
       </c>
       <c r="J10" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K10" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01558768251282838</v>
+        <v>0.01566825709026642</v>
       </c>
       <c r="M10" t="n">
-        <v>3.020344805138307</v>
+        <v>3.015697997777447</v>
       </c>
       <c r="N10" t="n">
-        <v>15.00054043831392</v>
+        <v>14.97639301050466</v>
       </c>
       <c r="O10" t="n">
-        <v>3.873053115865302</v>
+        <v>3.869934496926875</v>
       </c>
       <c r="P10" t="n">
-        <v>393.1423567600804</v>
+        <v>393.1429561995205</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39311,28 +39372,28 @@
         <v>0.0406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06155724762672007</v>
+        <v>0.06079460886772862</v>
       </c>
       <c r="J11" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K11" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01170255632358785</v>
+        <v>0.01145217064274529</v>
       </c>
       <c r="M11" t="n">
-        <v>3.246122817193402</v>
+        <v>3.24431702756269</v>
       </c>
       <c r="N11" t="n">
-        <v>17.27540869985656</v>
+        <v>17.25635988330222</v>
       </c>
       <c r="O11" t="n">
-        <v>4.15636965389949</v>
+        <v>4.15407750087817</v>
       </c>
       <c r="P11" t="n">
-        <v>391.0834100078119</v>
+        <v>391.091619892935</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39389,28 +39450,28 @@
         <v>0.0457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08021883879956937</v>
+        <v>-0.08025776132325496</v>
       </c>
       <c r="J12" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K12" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02042681888572584</v>
+        <v>0.02051768677147359</v>
       </c>
       <c r="M12" t="n">
-        <v>3.240824841172069</v>
+        <v>3.235750130914036</v>
       </c>
       <c r="N12" t="n">
-        <v>16.65911409488211</v>
+        <v>16.632267516133</v>
       </c>
       <c r="O12" t="n">
-        <v>4.081557802467351</v>
+        <v>4.078267710208956</v>
       </c>
       <c r="P12" t="n">
-        <v>390.4306998399755</v>
+        <v>390.4311188449689</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -39467,28 +39528,28 @@
         <v>0.0416</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1052374902737029</v>
+        <v>-0.1053642353423956</v>
       </c>
       <c r="J13" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K13" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03914141350492339</v>
+        <v>0.03936592669270966</v>
       </c>
       <c r="M13" t="n">
-        <v>3.029216143950251</v>
+        <v>3.024864597860952</v>
       </c>
       <c r="N13" t="n">
-        <v>14.67665032786185</v>
+        <v>14.65322177488919</v>
       </c>
       <c r="O13" t="n">
-        <v>3.831011658539014</v>
+        <v>3.827952687127833</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5005839461288</v>
+        <v>389.5019483699031</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -39545,28 +39606,28 @@
         <v>0.0362</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1252143254989395</v>
+        <v>-0.1257727634414405</v>
       </c>
       <c r="J14" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K14" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03042146481744556</v>
+        <v>0.0307859800630812</v>
       </c>
       <c r="M14" t="n">
-        <v>4.191723542172005</v>
+        <v>4.186981234401168</v>
       </c>
       <c r="N14" t="n">
-        <v>26.97577431459186</v>
+        <v>26.9369913077216</v>
       </c>
       <c r="O14" t="n">
-        <v>5.193820781909197</v>
+        <v>5.190085867085592</v>
       </c>
       <c r="P14" t="n">
-        <v>393.6102771928713</v>
+        <v>393.6162888350837</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -39604,7 +39665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O620"/>
+  <dimension ref="A1:O621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87347,6 +87408,83 @@
         </is>
       </c>
     </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>-36.67997225561943,174.74908330618996</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>-36.68067141433107,174.74940335643393</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>-36.68137308895437,174.7496873660797</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>-36.68206835364686,174.74998432592415</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>-36.6827593741161,174.75026767072063</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-36.683425843329765,174.7505456117875</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>-36.684103104164656,174.7508250938374</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>-36.684774554015114,174.75115169262992</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>-36.68545832637971,174.7514346875571</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>-36.68613266585468,174.7517088817814</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>-36.6867874891296,174.75203619971683</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>-36.6874433403315,174.7523975816363</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>-36.68808643683056,174.7528023867524</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0151/nzd0151.xlsx
+++ b/data/nzd0151/nzd0151.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O621"/>
+  <dimension ref="A1:O629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32123,6 +32123,414 @@
         <v>388.56</v>
       </c>
       <c r="O621" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>398.51</v>
+      </c>
+      <c r="C622" t="n">
+        <v>385.22</v>
+      </c>
+      <c r="D622" t="n">
+        <v>378.64</v>
+      </c>
+      <c r="E622" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="F622" t="n">
+        <v>384.24</v>
+      </c>
+      <c r="G622" t="n">
+        <v>388.17</v>
+      </c>
+      <c r="H622" t="n">
+        <v>387.99</v>
+      </c>
+      <c r="I622" t="n">
+        <v>391.18</v>
+      </c>
+      <c r="J622" t="n">
+        <v>391.36</v>
+      </c>
+      <c r="K622" t="n">
+        <v>390.58</v>
+      </c>
+      <c r="L622" t="n">
+        <v>389.06</v>
+      </c>
+      <c r="M622" t="n">
+        <v>387.04</v>
+      </c>
+      <c r="N622" t="n">
+        <v>389.39</v>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>398.17</v>
+      </c>
+      <c r="C623" t="n">
+        <v>383.92</v>
+      </c>
+      <c r="D623" t="n">
+        <v>377.42</v>
+      </c>
+      <c r="E623" t="n">
+        <v>373.21</v>
+      </c>
+      <c r="F623" t="n">
+        <v>383.69</v>
+      </c>
+      <c r="G623" t="n">
+        <v>386.51</v>
+      </c>
+      <c r="H623" t="n">
+        <v>386.56</v>
+      </c>
+      <c r="I623" t="n">
+        <v>389.93</v>
+      </c>
+      <c r="J623" t="n">
+        <v>390.63</v>
+      </c>
+      <c r="K623" t="n">
+        <v>390.44</v>
+      </c>
+      <c r="L623" t="n">
+        <v>388.38</v>
+      </c>
+      <c r="M623" t="n">
+        <v>386.26</v>
+      </c>
+      <c r="N623" t="n">
+        <v>388.45</v>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>396.46</v>
+      </c>
+      <c r="C624" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="D624" t="n">
+        <v>376.17</v>
+      </c>
+      <c r="E624" t="n">
+        <v>372.26</v>
+      </c>
+      <c r="F624" t="n">
+        <v>383.01</v>
+      </c>
+      <c r="G624" t="n">
+        <v>386.56</v>
+      </c>
+      <c r="H624" t="n">
+        <v>386.17</v>
+      </c>
+      <c r="I624" t="n">
+        <v>389.32</v>
+      </c>
+      <c r="J624" t="n">
+        <v>390.36</v>
+      </c>
+      <c r="K624" t="n">
+        <v>389.98</v>
+      </c>
+      <c r="L624" t="n">
+        <v>387.86</v>
+      </c>
+      <c r="M624" t="n">
+        <v>385.66</v>
+      </c>
+      <c r="N624" t="n">
+        <v>387.6</v>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>397.66</v>
+      </c>
+      <c r="C625" t="n">
+        <v>383.31</v>
+      </c>
+      <c r="D625" t="n">
+        <v>376.98</v>
+      </c>
+      <c r="E625" t="n">
+        <v>373.43</v>
+      </c>
+      <c r="F625" t="n">
+        <v>384.31</v>
+      </c>
+      <c r="G625" t="n">
+        <v>387.81</v>
+      </c>
+      <c r="H625" t="n">
+        <v>386.97</v>
+      </c>
+      <c r="I625" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="J625" t="n">
+        <v>390.49</v>
+      </c>
+      <c r="K625" t="n">
+        <v>390.76</v>
+      </c>
+      <c r="L625" t="n">
+        <v>388.26</v>
+      </c>
+      <c r="M625" t="n">
+        <v>385.87</v>
+      </c>
+      <c r="N625" t="n">
+        <v>387.62</v>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>396.06</v>
+      </c>
+      <c r="C626" t="n">
+        <v>381.79</v>
+      </c>
+      <c r="D626" t="n">
+        <v>375.69</v>
+      </c>
+      <c r="E626" t="n">
+        <v>372.06</v>
+      </c>
+      <c r="F626" t="n">
+        <v>383.07</v>
+      </c>
+      <c r="G626" t="n">
+        <v>386.56</v>
+      </c>
+      <c r="H626" t="n">
+        <v>386.04</v>
+      </c>
+      <c r="I626" t="n">
+        <v>388.78</v>
+      </c>
+      <c r="J626" t="n">
+        <v>389.73</v>
+      </c>
+      <c r="K626" t="n">
+        <v>390.45</v>
+      </c>
+      <c r="L626" t="n">
+        <v>388.01</v>
+      </c>
+      <c r="M626" t="n">
+        <v>385.23</v>
+      </c>
+      <c r="N626" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>396.02</v>
+      </c>
+      <c r="C627" t="n">
+        <v>381.24</v>
+      </c>
+      <c r="D627" t="n">
+        <v>375.34</v>
+      </c>
+      <c r="E627" t="n">
+        <v>371.98</v>
+      </c>
+      <c r="F627" t="n">
+        <v>382.63</v>
+      </c>
+      <c r="G627" t="n">
+        <v>385.78</v>
+      </c>
+      <c r="H627" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="I627" t="n">
+        <v>388.07</v>
+      </c>
+      <c r="J627" t="n">
+        <v>389.4</v>
+      </c>
+      <c r="K627" t="n">
+        <v>390.06</v>
+      </c>
+      <c r="L627" t="n">
+        <v>387.52</v>
+      </c>
+      <c r="M627" t="n">
+        <v>384.8</v>
+      </c>
+      <c r="N627" t="n">
+        <v>386.36</v>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>395.14</v>
+      </c>
+      <c r="C628" t="n">
+        <v>380.64</v>
+      </c>
+      <c r="D628" t="n">
+        <v>374.7</v>
+      </c>
+      <c r="E628" t="n">
+        <v>371.49</v>
+      </c>
+      <c r="F628" t="n">
+        <v>382.12</v>
+      </c>
+      <c r="G628" t="n">
+        <v>385.4</v>
+      </c>
+      <c r="H628" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="I628" t="n">
+        <v>387.75</v>
+      </c>
+      <c r="J628" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="K628" t="n">
+        <v>390.17</v>
+      </c>
+      <c r="L628" t="n">
+        <v>387.54</v>
+      </c>
+      <c r="M628" t="n">
+        <v>385</v>
+      </c>
+      <c r="N628" t="n">
+        <v>386.46</v>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>395.14</v>
+      </c>
+      <c r="C629" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="D629" t="n">
+        <v>375.46</v>
+      </c>
+      <c r="E629" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="F629" t="n">
+        <v>382.38</v>
+      </c>
+      <c r="G629" t="n">
+        <v>385.29</v>
+      </c>
+      <c r="H629" t="n">
+        <v>385.4</v>
+      </c>
+      <c r="I629" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="J629" t="n">
+        <v>389.29</v>
+      </c>
+      <c r="K629" t="n">
+        <v>390.26</v>
+      </c>
+      <c r="L629" t="n">
+        <v>387.15</v>
+      </c>
+      <c r="M629" t="n">
+        <v>384.44</v>
+      </c>
+      <c r="N629" t="n">
+        <v>385.64</v>
+      </c>
+      <c r="O629" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32139,7 +32547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B636"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38502,6 +38910,86 @@
       </c>
       <c r="B636" t="n">
         <v>-0.85</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>-0.86</v>
       </c>
     </row>
   </sheetData>
@@ -38670,28 +39158,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2204228376421573</v>
+        <v>-0.2429943846798817</v>
       </c>
       <c r="J2" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K2" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0615877475689437</v>
+        <v>0.07406678835200431</v>
       </c>
       <c r="M2" t="n">
-        <v>5.124366779691348</v>
+        <v>5.177601757360119</v>
       </c>
       <c r="N2" t="n">
-        <v>40.04254777130707</v>
+        <v>40.53656079518211</v>
       </c>
       <c r="O2" t="n">
-        <v>6.327918122993302</v>
+        <v>6.36683287005259</v>
       </c>
       <c r="P2" t="n">
-        <v>411.5059079417449</v>
+        <v>411.7496107370906</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38748,28 +39236,28 @@
         <v>0.0257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.225248987599705</v>
+        <v>-0.2341773794366945</v>
       </c>
       <c r="J3" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K3" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06254221485854716</v>
+        <v>0.06875333050030885</v>
       </c>
       <c r="M3" t="n">
-        <v>5.24779434571303</v>
+        <v>5.224721908008765</v>
       </c>
       <c r="N3" t="n">
-        <v>41.13517355635635</v>
+        <v>40.79051147042858</v>
       </c>
       <c r="O3" t="n">
-        <v>6.413670833177857</v>
+        <v>6.386744982416989</v>
       </c>
       <c r="P3" t="n">
-        <v>392.0961449655576</v>
+        <v>392.1925676149921</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38826,28 +39314,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2492029882412534</v>
+        <v>-0.2511305452478759</v>
       </c>
       <c r="J4" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K4" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09452355015125458</v>
+        <v>0.09823267320807239</v>
       </c>
       <c r="M4" t="n">
-        <v>4.656744067737833</v>
+        <v>4.613750564064735</v>
       </c>
       <c r="N4" t="n">
-        <v>32.17753727113275</v>
+        <v>31.79332049164662</v>
       </c>
       <c r="O4" t="n">
-        <v>5.672524770429192</v>
+        <v>5.638556596474547</v>
       </c>
       <c r="P4" t="n">
-        <v>383.7169664980367</v>
+        <v>383.73780815599</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38904,28 +39392,28 @@
         <v>0.0317</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2280612693258778</v>
+        <v>-0.2257013314077088</v>
       </c>
       <c r="J5" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K5" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09107296891084504</v>
+        <v>0.09161075042009936</v>
       </c>
       <c r="M5" t="n">
-        <v>4.329606287211117</v>
+        <v>4.283482407083729</v>
       </c>
       <c r="N5" t="n">
-        <v>28.07706936850662</v>
+        <v>27.73908063159</v>
       </c>
       <c r="O5" t="n">
-        <v>5.2987799886867</v>
+        <v>5.266790353867334</v>
       </c>
       <c r="P5" t="n">
-        <v>377.6106537403965</v>
+        <v>377.5851995202246</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38982,28 +39470,28 @@
         <v>0.0356</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2116688918128711</v>
+        <v>-0.2068876700279977</v>
       </c>
       <c r="J6" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K6" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07271473161183672</v>
+        <v>0.07141752925684541</v>
       </c>
       <c r="M6" t="n">
-        <v>4.387792499100928</v>
+        <v>4.350633876788454</v>
       </c>
       <c r="N6" t="n">
-        <v>30.90396496187532</v>
+        <v>30.56209720114295</v>
       </c>
       <c r="O6" t="n">
-        <v>5.559133472212673</v>
+        <v>5.528299666366047</v>
       </c>
       <c r="P6" t="n">
-        <v>386.9299589232757</v>
+        <v>386.8783627085446</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39060,28 +39548,28 @@
         <v>0.0358</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2547543679437022</v>
+        <v>-0.2524288084091689</v>
       </c>
       <c r="J7" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K7" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L7" t="n">
-        <v>0.105634666068243</v>
+        <v>0.1064766881101243</v>
       </c>
       <c r="M7" t="n">
-        <v>4.179013778244697</v>
+        <v>4.135372062054936</v>
       </c>
       <c r="N7" t="n">
-        <v>29.72083095090037</v>
+        <v>29.3648281523155</v>
       </c>
       <c r="O7" t="n">
-        <v>5.451681479222752</v>
+        <v>5.418932381227458</v>
       </c>
       <c r="P7" t="n">
-        <v>392.3848078459183</v>
+        <v>392.3597277674368</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39138,28 +39626,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.262619714170868</v>
+        <v>-0.2615270028672764</v>
       </c>
       <c r="J8" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K8" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1258713695742206</v>
+        <v>0.1279886839367307</v>
       </c>
       <c r="M8" t="n">
-        <v>3.886275842756619</v>
+        <v>3.846651682226312</v>
       </c>
       <c r="N8" t="n">
-        <v>25.90670690452206</v>
+        <v>25.59068415441769</v>
       </c>
       <c r="O8" t="n">
-        <v>5.089863151846232</v>
+        <v>5.058723569678194</v>
       </c>
       <c r="P8" t="n">
-        <v>392.7195615422965</v>
+        <v>392.7077912410144</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39216,28 +39704,28 @@
         <v>0.0367</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1258457400745759</v>
+        <v>-0.1258402083714323</v>
       </c>
       <c r="J9" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K9" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03997815053564113</v>
+        <v>0.04103516531619811</v>
       </c>
       <c r="M9" t="n">
-        <v>3.452780388977894</v>
+        <v>3.420346284135543</v>
       </c>
       <c r="N9" t="n">
-        <v>20.57048978758659</v>
+        <v>20.3228039536952</v>
       </c>
       <c r="O9" t="n">
-        <v>4.535470183739123</v>
+        <v>4.50808207042587</v>
       </c>
       <c r="P9" t="n">
-        <v>392.5161886848607</v>
+        <v>392.5161587452359</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39294,28 +39782,28 @@
         <v>0.0357</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06638785327333588</v>
+        <v>-0.06966649502380369</v>
       </c>
       <c r="J10" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K10" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01566825709026642</v>
+        <v>0.01767530928020655</v>
       </c>
       <c r="M10" t="n">
-        <v>3.015697997777447</v>
+        <v>2.990477569309164</v>
       </c>
       <c r="N10" t="n">
-        <v>14.97639301050466</v>
+        <v>14.81270033212981</v>
       </c>
       <c r="O10" t="n">
-        <v>3.869934496926875</v>
+        <v>3.848727105437564</v>
       </c>
       <c r="P10" t="n">
-        <v>393.1429561995205</v>
+        <v>393.1783716991376</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39372,28 +39860,28 @@
         <v>0.0406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06079460886772862</v>
+        <v>0.05481700064386947</v>
       </c>
       <c r="J11" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K11" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01145217064274529</v>
+        <v>0.009554313333297482</v>
       </c>
       <c r="M11" t="n">
-        <v>3.24431702756269</v>
+        <v>3.229751694301778</v>
       </c>
       <c r="N11" t="n">
-        <v>17.25635988330222</v>
+        <v>17.10645420466129</v>
       </c>
       <c r="O11" t="n">
-        <v>4.15407750087817</v>
+        <v>4.135994947368927</v>
       </c>
       <c r="P11" t="n">
-        <v>391.091619892935</v>
+        <v>391.156153469886</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39450,28 +39938,28 @@
         <v>0.0457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08025776132325496</v>
+        <v>-0.08105607906850147</v>
       </c>
       <c r="J12" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K12" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02051768677147359</v>
+        <v>0.02149377287233389</v>
       </c>
       <c r="M12" t="n">
-        <v>3.235750130914036</v>
+        <v>3.200372283615982</v>
       </c>
       <c r="N12" t="n">
-        <v>16.632267516133</v>
+        <v>16.42556804825662</v>
       </c>
       <c r="O12" t="n">
-        <v>4.078267710208956</v>
+        <v>4.052846906590061</v>
       </c>
       <c r="P12" t="n">
-        <v>390.4311188449689</v>
+        <v>390.4397534852343</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -39528,28 +40016,28 @@
         <v>0.0416</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1053642353423956</v>
+        <v>-0.108259965609749</v>
       </c>
       <c r="J13" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K13" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03936592669270966</v>
+        <v>0.04252759997293143</v>
       </c>
       <c r="M13" t="n">
-        <v>3.024864597860952</v>
+        <v>2.999540944804918</v>
       </c>
       <c r="N13" t="n">
-        <v>14.65322177488919</v>
+        <v>14.49070232573627</v>
       </c>
       <c r="O13" t="n">
-        <v>3.827952687127833</v>
+        <v>3.806665512720584</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5019483699031</v>
+        <v>389.5332331319602</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -39606,28 +40094,28 @@
         <v>0.0362</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1257727634414405</v>
+        <v>-0.1331483024637016</v>
       </c>
       <c r="J14" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K14" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0307859800630812</v>
+        <v>0.03516141930883221</v>
       </c>
       <c r="M14" t="n">
-        <v>4.186981234401168</v>
+        <v>4.160066696595079</v>
       </c>
       <c r="N14" t="n">
-        <v>26.9369913077216</v>
+        <v>26.71516171332244</v>
       </c>
       <c r="O14" t="n">
-        <v>5.190085867085592</v>
+        <v>5.168671174811031</v>
       </c>
       <c r="P14" t="n">
-        <v>393.6162888350837</v>
+        <v>393.6959461113398</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -39665,7 +40153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O621"/>
+  <dimension ref="A1:O629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87485,6 +87973,622 @@
         </is>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-36.67997585185038,174.74907567748392</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>-36.68067291417063,174.74939965893273</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>-36.68137461133406,174.74968294158677</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>-36.68206888985665,174.74998218940746</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>-36.682759632106986,174.7502663667736</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>-36.68342677704825,174.75054198833462</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>-36.684103104164656,174.7508250938374</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>-36.68477598688279,174.75114662483747</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>-36.68545784875429,174.7514363768347</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>-36.6861319986842,174.75171096077707</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>-36.686784103699146,174.75204522811092</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>-36.68744047450871,174.7524049345441</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>-36.68808317840945,174.7528107469639</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-36.6799773995952,174.74907239424311</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>-36.68067818387629,174.74938666771106</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>-36.68137893064291,174.7496703883732</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>-36.682070471675324,174.74997588668307</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>-36.682760814565036,174.75026039034947</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>-36.6834313357899,174.75052429735743</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>-36.684107372885066,174.7508099961543</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>-36.68477971830804,174.75113342746036</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>-36.685460027920094,174.75142866950532</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>-36.68613246570354,174.7517095054801</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>-36.68678669032022,174.75203833001214</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>-36.68744353662072,174.75239707801245</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>-36.68808686866945,174.7528012787725</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-36.67998518383988,174.74905588147115</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>-36.680684588593614,174.74937087837768</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>-36.681383356162954,174.74965752647256</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>-36.6820730186708,174.74996573822798</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>-36.68276227651273,174.75025300131574</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>-36.683431198478445,174.7505248302182</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>-36.68410853708121,174.75080587860407</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>-36.68478153924304,174.75112698713986</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>-36.6854608339128,174.75142581884913</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>-36.686134000195516,174.75170472378994</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>-36.6867886683243,174.7520330549951</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>-36.68744589209114,174.75239103452614</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>-36.68809020560605,174.75279271710926</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-36.679979721212256,174.74906746938166</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>-36.680680656583846,174.7493805718295</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>-36.68138048842612,174.74966586098435</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>-36.68206988184467,174.74997823685152</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>-36.68275948161232,174.75026712740936</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>-36.68342776569123,174.75053815173732</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>-36.6841061489864,174.7508143248608</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>-36.68477995711922,174.75113258282818</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>-36.68546044584225,174.7514271913873</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>-36.68613139823075,174.75171283187314</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>-36.68678714678273,174.75203711270055</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>-36.68744506767653,174.7523931497464</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>-36.6880901270899,174.75279291856017</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-36.679987004715514,174.74905201883396</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-36.68068681808335,174.7493653820901</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>-36.68138505556229,174.7496525875023</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>-36.682073554880276,174.74996360171104</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>-36.682762147517366,174.75025365328932</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>-36.683431198478445,174.7505248302182</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>-36.68410892514657,174.75080450608732</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>-36.684783151218,174.75112128587224</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>-36.68546271456219,174.75141916731778</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>-36.686132432345026,174.7517096094299</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>-36.68678809774623,174.75203457663466</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>-36.687447580178095,174.7523867033607</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>-36.688092168509655,174.7527876808364</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-36.67998718680307,174.74905163257023</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-36.680689047572834,174.74935988580222</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>-36.68138629470751,174.7496489861697</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>-36.68207376936406,174.74996274710426</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>-36.68276309348331,174.7502488721497</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>-36.68343334053691,174.75051651758963</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>-36.68411158190124,174.75079510962595</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>-36.684785270666154,174.75111378976075</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>-36.68546369966411,174.75141568318216</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>-36.68613373332737,174.75170555538824</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>-36.68678996163454,174.75202960594535</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>-36.68744926826491,174.7523823721951</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>-36.68809507360661,174.7527802271521</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-36.679991192729005,174.74904313476767</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-36.6806914797429,174.74935388985142</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>-36.68138856057279,174.74964240087547</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>-36.68207508307705,174.74995751263756</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>-36.68276418994361,174.7502433303741</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>-36.683434384103656,174.75051246784733</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>-36.68411238788286,174.75079225901393</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>-36.68478622591025,174.7511104112315</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>-36.68546399817983,174.75141462738347</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>-36.686133366383636,174.7517066988359</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>-36.68678988555747,174.75202980883066</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>-36.68744848310827,174.75238438669075</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>-36.688094681025966,174.75278123440677</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-36.679991192729005,174.74904313476767</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-36.680686737011,174.74936558195512</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>-36.68138586985773,174.74965022091232</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-36.682075136697975,174.74995729898586</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>-36.68276363096389,174.75024615559306</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>-36.68343468618875,174.7505112955535</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>-36.6841108356219,174.75079774908144</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>-36.684784285570586,174.75111727386897</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>-36.6854640280314,174.7514145218036</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>-36.686133066156955,174.75170763438396</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>-36.68679136906027,174.75202585256756</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>-36.68745068154676,174.7523787461028</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>-36.688097900186996,174.7527729749182</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0151/nzd0151.xlsx
+++ b/data/nzd0151/nzd0151.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O629"/>
+  <dimension ref="A1:O632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32492,7 +32492,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>395.14</v>
+        <v>396.85</v>
       </c>
       <c r="C629" t="n">
         <v>381.81</v>
@@ -32531,6 +32531,159 @@
         <v>385.64</v>
       </c>
       <c r="O629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>397.28</v>
+      </c>
+      <c r="C630" t="n">
+        <v>380.76</v>
+      </c>
+      <c r="D630" t="n">
+        <v>374.95</v>
+      </c>
+      <c r="E630" t="n">
+        <v>370.85</v>
+      </c>
+      <c r="F630" t="n">
+        <v>382.31</v>
+      </c>
+      <c r="G630" t="n">
+        <v>384.23</v>
+      </c>
+      <c r="H630" t="n">
+        <v>384.89</v>
+      </c>
+      <c r="I630" t="n">
+        <v>387.88</v>
+      </c>
+      <c r="J630" t="n">
+        <v>388.86</v>
+      </c>
+      <c r="K630" t="n">
+        <v>389.71</v>
+      </c>
+      <c r="L630" t="n">
+        <v>386.47</v>
+      </c>
+      <c r="M630" t="n">
+        <v>382.96</v>
+      </c>
+      <c r="N630" t="n">
+        <v>383.47</v>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>398.86</v>
+      </c>
+      <c r="C631" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="D631" t="n">
+        <v>375.78</v>
+      </c>
+      <c r="E631" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="F631" t="n">
+        <v>382.91</v>
+      </c>
+      <c r="G631" t="n">
+        <v>385.31</v>
+      </c>
+      <c r="H631" t="n">
+        <v>385.76</v>
+      </c>
+      <c r="I631" t="n">
+        <v>388.8</v>
+      </c>
+      <c r="J631" t="n">
+        <v>389.18</v>
+      </c>
+      <c r="K631" t="n">
+        <v>389.92</v>
+      </c>
+      <c r="L631" t="n">
+        <v>386.58</v>
+      </c>
+      <c r="M631" t="n">
+        <v>382.71</v>
+      </c>
+      <c r="N631" t="n">
+        <v>382.82</v>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>399.09</v>
+      </c>
+      <c r="C632" t="n">
+        <v>382.09</v>
+      </c>
+      <c r="D632" t="n">
+        <v>375.56</v>
+      </c>
+      <c r="E632" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="F632" t="n">
+        <v>382.69</v>
+      </c>
+      <c r="G632" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="H632" t="n">
+        <v>385.55</v>
+      </c>
+      <c r="I632" t="n">
+        <v>388.47</v>
+      </c>
+      <c r="J632" t="n">
+        <v>388.89</v>
+      </c>
+      <c r="K632" t="n">
+        <v>389.75</v>
+      </c>
+      <c r="L632" t="n">
+        <v>386.37</v>
+      </c>
+      <c r="M632" t="n">
+        <v>382.1</v>
+      </c>
+      <c r="N632" t="n">
+        <v>382.03</v>
+      </c>
+      <c r="O632" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32547,7 +32700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B644"/>
+  <dimension ref="A1:B647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38990,6 +39143,36 @@
       </c>
       <c r="B644" t="n">
         <v>-0.86</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -39158,28 +39341,28 @@
         <v>0.0203</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2429943846798817</v>
+        <v>-0.2488629308012003</v>
       </c>
       <c r="J2" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K2" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07406678835200431</v>
+        <v>0.07784138625918813</v>
       </c>
       <c r="M2" t="n">
-        <v>5.177601757360119</v>
+        <v>5.18399567483924</v>
       </c>
       <c r="N2" t="n">
-        <v>40.53656079518211</v>
+        <v>40.51559830539987</v>
       </c>
       <c r="O2" t="n">
-        <v>6.36683287005259</v>
+        <v>6.365186431315258</v>
       </c>
       <c r="P2" t="n">
-        <v>411.7496107370906</v>
+        <v>411.8132524489489</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39236,28 +39419,28 @@
         <v>0.0257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2341773794366945</v>
+        <v>-0.2381118015261721</v>
       </c>
       <c r="J3" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K3" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06875333050030885</v>
+        <v>0.07146176339929511</v>
       </c>
       <c r="M3" t="n">
-        <v>5.224721908008765</v>
+        <v>5.219089326061108</v>
       </c>
       <c r="N3" t="n">
-        <v>40.79051147042858</v>
+        <v>40.68128603210236</v>
       </c>
       <c r="O3" t="n">
-        <v>6.386744982416989</v>
+        <v>6.378188303280357</v>
       </c>
       <c r="P3" t="n">
-        <v>392.1925676149921</v>
+        <v>392.2352254597546</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39314,28 +39497,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2511305452478759</v>
+        <v>-0.2526094041877168</v>
       </c>
       <c r="J4" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K4" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09823267320807239</v>
+        <v>0.1001688138640326</v>
       </c>
       <c r="M4" t="n">
-        <v>4.613750564064735</v>
+        <v>4.599616039756229</v>
       </c>
       <c r="N4" t="n">
-        <v>31.79332049164662</v>
+        <v>31.65441608923604</v>
       </c>
       <c r="O4" t="n">
-        <v>5.638556596474547</v>
+        <v>5.626225741048438</v>
       </c>
       <c r="P4" t="n">
-        <v>383.73780815599</v>
+        <v>383.7538422480238</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39392,28 +39575,28 @@
         <v>0.0317</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2257013314077088</v>
+        <v>-0.2265786782292212</v>
       </c>
       <c r="J5" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K5" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09161075042009936</v>
+        <v>0.0931115890292924</v>
       </c>
       <c r="M5" t="n">
-        <v>4.283482407083729</v>
+        <v>4.268659037323869</v>
       </c>
       <c r="N5" t="n">
-        <v>27.73908063159</v>
+        <v>27.61181531308952</v>
       </c>
       <c r="O5" t="n">
-        <v>5.266790353867334</v>
+        <v>5.254694597508928</v>
       </c>
       <c r="P5" t="n">
-        <v>377.5851995202246</v>
+        <v>377.5947156105184</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39470,28 +39653,28 @@
         <v>0.0356</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2068876700279977</v>
+        <v>-0.2056669080993982</v>
       </c>
       <c r="J6" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K6" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07141752925684541</v>
+        <v>0.07129855262044993</v>
       </c>
       <c r="M6" t="n">
-        <v>4.350633876788454</v>
+        <v>4.334731413183802</v>
       </c>
       <c r="N6" t="n">
-        <v>30.56209720114295</v>
+        <v>30.42503000055117</v>
       </c>
       <c r="O6" t="n">
-        <v>5.528299666366047</v>
+        <v>5.515888867675923</v>
       </c>
       <c r="P6" t="n">
-        <v>386.8783627085446</v>
+        <v>386.8651255438494</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39548,28 +39731,28 @@
         <v>0.0358</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2524288084091689</v>
+        <v>-0.2530480477169068</v>
       </c>
       <c r="J7" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K7" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1064766881101243</v>
+        <v>0.1079220038256939</v>
       </c>
       <c r="M7" t="n">
-        <v>4.135372062054936</v>
+        <v>4.119771120470715</v>
       </c>
       <c r="N7" t="n">
-        <v>29.3648281523155</v>
+        <v>29.22843599813909</v>
       </c>
       <c r="O7" t="n">
-        <v>5.418932381227458</v>
+        <v>5.406332952948707</v>
       </c>
       <c r="P7" t="n">
-        <v>392.3597277674368</v>
+        <v>392.3664397561977</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39626,28 +39809,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2615270028672764</v>
+        <v>-0.2618035340260235</v>
       </c>
       <c r="J8" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K8" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1279886839367307</v>
+        <v>0.1293771319315855</v>
       </c>
       <c r="M8" t="n">
-        <v>3.846651682226312</v>
+        <v>3.830193019327973</v>
       </c>
       <c r="N8" t="n">
-        <v>25.59068415441769</v>
+        <v>25.47008113785877</v>
       </c>
       <c r="O8" t="n">
-        <v>5.058723569678194</v>
+        <v>5.04678919094693</v>
       </c>
       <c r="P8" t="n">
-        <v>392.7077912410144</v>
+        <v>392.7107884267554</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39704,28 +39887,28 @@
         <v>0.0367</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1258402083714323</v>
+        <v>-0.1265521501129862</v>
       </c>
       <c r="J9" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K9" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04103516531619811</v>
+        <v>0.04188667999679607</v>
       </c>
       <c r="M9" t="n">
-        <v>3.420346284135543</v>
+        <v>3.407472250979841</v>
       </c>
       <c r="N9" t="n">
-        <v>20.3228039536952</v>
+        <v>20.22957521929251</v>
       </c>
       <c r="O9" t="n">
-        <v>4.50808207042587</v>
+        <v>4.497730007380668</v>
       </c>
       <c r="P9" t="n">
-        <v>392.5161587452359</v>
+        <v>392.5238774883636</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39782,28 +39965,28 @@
         <v>0.0357</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06966649502380369</v>
+        <v>-0.0718564695581189</v>
       </c>
       <c r="J10" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K10" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01767530928020655</v>
+        <v>0.0189414871176059</v>
       </c>
       <c r="M10" t="n">
-        <v>2.990477569309164</v>
+        <v>2.985040337601669</v>
       </c>
       <c r="N10" t="n">
-        <v>14.81270033212981</v>
+        <v>14.76792088808547</v>
       </c>
       <c r="O10" t="n">
-        <v>3.848727105437564</v>
+        <v>3.842905266603052</v>
       </c>
       <c r="P10" t="n">
-        <v>393.1783716991376</v>
+        <v>393.2021178913475</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39860,28 +40043,28 @@
         <v>0.0406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05481700064386947</v>
+        <v>0.05216239517804312</v>
       </c>
       <c r="J11" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K11" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009554313333297482</v>
+        <v>0.008729035253426831</v>
       </c>
       <c r="M11" t="n">
-        <v>3.229751694301778</v>
+        <v>3.226435185900079</v>
       </c>
       <c r="N11" t="n">
-        <v>17.10645420466129</v>
+        <v>17.06270790247819</v>
       </c>
       <c r="O11" t="n">
-        <v>4.135994947368927</v>
+        <v>4.130703076048699</v>
       </c>
       <c r="P11" t="n">
-        <v>391.156153469886</v>
+        <v>391.1849374225008</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39938,28 +40121,28 @@
         <v>0.0457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08105607906850147</v>
+        <v>-0.0827375469575478</v>
       </c>
       <c r="J12" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K12" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02149377287233389</v>
+        <v>0.02258090169814175</v>
       </c>
       <c r="M12" t="n">
-        <v>3.200372283615982</v>
+        <v>3.191717228900505</v>
       </c>
       <c r="N12" t="n">
-        <v>16.42556804825662</v>
+        <v>16.3625727251051</v>
       </c>
       <c r="O12" t="n">
-        <v>4.052846906590061</v>
+        <v>4.045067703401898</v>
       </c>
       <c r="P12" t="n">
-        <v>390.4397534852343</v>
+        <v>390.4579861952536</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40016,28 +40199,28 @@
         <v>0.0416</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.108259965609749</v>
+        <v>-0.1120471461031842</v>
       </c>
       <c r="J13" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K13" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04252759997293143</v>
+        <v>0.04563424616218215</v>
       </c>
       <c r="M13" t="n">
-        <v>2.999540944804918</v>
+        <v>3.001060052293236</v>
       </c>
       <c r="N13" t="n">
-        <v>14.49070232573627</v>
+        <v>14.4988091377896</v>
       </c>
       <c r="O13" t="n">
-        <v>3.806665512720584</v>
+        <v>3.807730181852386</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5332331319602</v>
+        <v>389.5743005033552</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -40094,28 +40277,28 @@
         <v>0.0362</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1331483024637016</v>
+        <v>-0.1400459229197512</v>
       </c>
       <c r="J14" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="K14" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03516141930883221</v>
+        <v>0.03878245650128642</v>
       </c>
       <c r="M14" t="n">
-        <v>4.160066696595079</v>
+        <v>4.164872187292342</v>
       </c>
       <c r="N14" t="n">
-        <v>26.71516171332244</v>
+        <v>26.84318735829758</v>
       </c>
       <c r="O14" t="n">
-        <v>5.168671174811031</v>
+        <v>5.181041146169134</v>
       </c>
       <c r="P14" t="n">
-        <v>393.6959461113398</v>
+        <v>393.7707415146275</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -40153,7 +40336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O629"/>
+  <dimension ref="A1:O632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88520,7 +88703,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>-36.679991192729005,174.74904313476767</t>
+          <t>-36.67998340848603,174.74905964754228</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -88584,6 +88767,237 @@
         </is>
       </c>
       <c r="O629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-36.679981451044455,174.74906379987686</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-36.680690993308914,174.74935508904161</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>-36.68138767546921,174.74964497325607</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-36.68207679894674,174.74995067578283</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>-36.682763781458426,174.75024539495718</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>-36.68343759718989,174.75049999890322</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>-36.68411235803168,174.75079236459214</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>-36.684785837842355,174.751111783759</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>-36.685465311648855,174.75140998186916</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>-36.686134900875516,174.75170191714565</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>-36.68679395568025,174.75201895446745</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>-36.68745649170438,174.75236383883302</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>-36.68810641918362,174.75275111748763</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-36.679974258583556,174.7490790572905</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-36.68068475073833,174.74937047864768</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>-36.681384736924926,174.74965351355925</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>-36.68207687937813,174.74995035530526</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-36.682762491505,174.7502519146931</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>-36.68343463126418,174.75051150869785</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>-36.68410976097957,174.7508015498973</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>-36.68478309151523,174.7511214970303</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>-36.68546435639866,174.75141336042503</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>-36.68613420034664,174.75170410009125</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>-36.686793537256456,174.7520200703366</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>-36.68745747314975,174.7523613207129</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>-36.688108970956044,174.75274457033007</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-36.67997321157959,174.74908127830616</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-36.68068560199807,174.7493683800652</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-36.68138551581624,174.74965124986448</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-36.68207872929969,174.74994298432088</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-36.682762964487964,174.7502495241233</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>-36.683434796037865,174.75051086926484</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>-36.68411038785429,174.75079933275472</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>-36.68478407661092,174.7511180129222</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>-36.68546522209416,174.7514102986088</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>-36.686134767441445,174.7517023329448</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>-36.68679433606551,174.75201794004093</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>-36.687459867876235,174.75235517649952</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>-36.68811207234051,174.75273661301486</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
